--- a/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="561">
   <si>
     <t>#</t>
   </si>
@@ -57,15 +57,9 @@
     <t>RF / Coaxial Connectors</t>
   </si>
   <si>
-    <t>Male Header</t>
-  </si>
-  <si>
     <t>Wire to Board Connector</t>
   </si>
   <si>
-    <t>Male Pin Header</t>
-  </si>
-  <si>
     <t>Inductors</t>
   </si>
   <si>
@@ -114,12 +108,6 @@
     <t>C3, C17, C22, C23, C34, C38, C42, C45, C87, C88</t>
   </si>
   <si>
-    <t>C4, C11, C16, C20, C33, C37, C41, C57, C58, C93, C94, C147, C149</t>
-  </si>
-  <si>
-    <t>C7, C12, C13, C14, C15, C18, C19, C24, C27, C28, C29, C30, C31, C35, C36, C39, C40, C43, C44, C46, C95, C97, C111, C114, C117, C120, C124, C127, C130, C133, C148</t>
-  </si>
-  <si>
     <t>C8</t>
   </si>
   <si>
@@ -228,21 +216,12 @@
     <t>J5, J6</t>
   </si>
   <si>
-    <t>J7</t>
-  </si>
-  <si>
     <t>J8</t>
   </si>
   <si>
-    <t>J9</t>
-  </si>
-  <si>
     <t>J10</t>
   </si>
   <si>
-    <t>J11</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
@@ -261,9 +240,6 @@
     <t>LED1</t>
   </si>
   <si>
-    <t>LED2, LED3, LED4, LED5, LED8, LED9</t>
-  </si>
-  <si>
     <t>LED6, LED11</t>
   </si>
   <si>
@@ -315,9 +291,6 @@
     <t>R17</t>
   </si>
   <si>
-    <t>R18, R19, R90, R91, R92, R94, R115</t>
-  </si>
-  <si>
     <t>R20</t>
   </si>
   <si>
@@ -438,9 +411,6 @@
     <t>R113, R119</t>
   </si>
   <si>
-    <t>R116</t>
-  </si>
-  <si>
     <t>R122</t>
   </si>
   <si>
@@ -498,9 +468,6 @@
     <t>U15</t>
   </si>
   <si>
-    <t>U16</t>
-  </si>
-  <si>
     <t>X1</t>
   </si>
   <si>
@@ -630,18 +597,9 @@
     <t>CONN U.FL RCPT STR 50 OHM SMD</t>
   </si>
   <si>
-    <t>Gold 250V 3A Policy 2.5mm 10P 260℃ -40℃~+105℃ 2.54mm Single Row Black Brass 2.54mm 1x10P Plugin,P=2.54mm Pin Headers ROHS</t>
-  </si>
-  <si>
-    <t>Gold 250V 3A Square Pins 2.5mm 12P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 2.54mm 1x12P Plugin,P=2.54mm Pin Headers ROHS</t>
-  </si>
-  <si>
     <t>CONN HEADER VERT 8POS 2.5MM</t>
   </si>
   <si>
-    <t>Gold 250V 3A Policy 2.5mm 8P -40℃~+105℃ 2.54mm Double Row Black Brass 2.54mm 2x4P Plugin,P=2.54mm Pin Headers ROHS</t>
-  </si>
-  <si>
     <t>FIXED IND 6.8UH 4.5A 50.16 MOHM</t>
   </si>
   <si>
@@ -822,9 +780,6 @@
     <t>RES SMD 4.7K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES 680 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
     <t>RES SMD 10M Ohm 5% 1/16W 0402</t>
   </si>
   <si>
@@ -882,9 +837,6 @@
     <t>IC TRANSLATOR BIDIR 20TSSOP</t>
   </si>
   <si>
-    <t>IC XPND 400KHZ I2C SMBUS 16TSSOP</t>
-  </si>
-  <si>
     <t>24MHz Surface Mount Crystal 12pF ±10ppm ±10ppm SMD3225-4P Crystals ROHS</t>
   </si>
   <si>
@@ -939,21 +891,9 @@
     <t>U.FL-R-SMT(10)</t>
   </si>
   <si>
-    <t>HDR 1X10 male</t>
-  </si>
-  <si>
-    <t>HDR 1x12 TH</t>
-  </si>
-  <si>
     <t>B8B-XH-A(LF)(SN)</t>
   </si>
   <si>
-    <t>HDR 2X4 (2.54mm Male)</t>
-  </si>
-  <si>
-    <t>ETQP3M6R8KVN</t>
-  </si>
-  <si>
     <t>SMNR4030-4R7MT</t>
   </si>
   <si>
@@ -1041,9 +981,6 @@
     <t>TSSOP-20</t>
   </si>
   <si>
-    <t>TSSOP_16</t>
-  </si>
-  <si>
     <t>SMD3225-4P</t>
   </si>
   <si>
@@ -1155,15 +1092,6 @@
     <t>BLM18PG221SN1D</t>
   </si>
   <si>
-    <t>X6511WV-10H-C60D30</t>
-  </si>
-  <si>
-    <t>X6511WV-12H-C60D30</t>
-  </si>
-  <si>
-    <t>X6521WV-2x04H-C60D30</t>
-  </si>
-  <si>
     <t>ETQ-P3M6R8KVN</t>
   </si>
   <si>
@@ -1329,9 +1257,6 @@
     <t>RC0603FR-074K7L</t>
   </si>
   <si>
-    <t>RC0402FR-07680RL</t>
-  </si>
-  <si>
     <t>RC0402JR-0710ML</t>
   </si>
   <si>
@@ -1377,9 +1302,6 @@
     <t>TXS0108EPWR</t>
   </si>
   <si>
-    <t>PCA9557PW,118</t>
-  </si>
-  <si>
     <t>7M24000192</t>
   </si>
   <si>
@@ -1428,9 +1350,6 @@
     <t>Hirose</t>
   </si>
   <si>
-    <t>XKB</t>
-  </si>
-  <si>
     <t>JST</t>
   </si>
   <si>
@@ -1578,18 +1497,6 @@
     <t>22uH</t>
   </si>
   <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>YELLOW</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
     <t>47K</t>
   </si>
   <si>
@@ -1732,13 +1639,76 @@
   </si>
   <si>
     <t>DO NOT PLACE</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>BWIPX1-SMA-1.13L200</t>
+  </si>
+  <si>
+    <t>20cm IPEX to SMA 1Gen RF Cables ROHS</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>MKUS008G-IGT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage products </t>
+  </si>
+  <si>
+    <t>MK</t>
+  </si>
+  <si>
+    <t>or any other industrial microSD card with 8GB of storage</t>
+  </si>
+  <si>
+    <t>JS05A-40P-100-3-4</t>
+  </si>
+  <si>
+    <t>JUSHUO</t>
+  </si>
+  <si>
+    <t>0.3mm 40P 0.5mm Same Side 10cm P=0.5mm FFC Cable (Flexible Flat Cable) ROHS</t>
+  </si>
+  <si>
+    <t>C4, C11, C16, C20, C33, C37, C41, C57, C58, C93, C94, C149</t>
+  </si>
+  <si>
+    <t>C7, C12, C13, C14, C15, C18, C19, C24, C27, C28, C29, C30, C31, C35, C36, C39, C40, C43, C44, C46, C95, C97, C111, C114, C117, C120, C124, C127, C130, C133</t>
+  </si>
+  <si>
+    <t>LED2, LED3, LED4, LED5, LED8</t>
+  </si>
+  <si>
+    <t>R18, R19, R90, R91, R92, R94</t>
+  </si>
+  <si>
+    <t>SD Card</t>
+  </si>
+  <si>
+    <t>3 4G Antenna 3.8dBi Linear 10W Antennas ROHS</t>
+  </si>
+  <si>
+    <t>AECW004</t>
+  </si>
+  <si>
+    <t>MyAntenna</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1792,6 +1762,14 @@
     <font>
       <b/>
       <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1914,7 +1892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1951,9 +1929,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1962,6 +1937,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2250,17 +2231,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
   </cols>
@@ -2274,9 +2255,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2287,28 +2268,28 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>566</v>
+        <v>535</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>567</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2321,22 +2302,22 @@
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="J3" s="7">
         <v>4</v>
@@ -2346,29 +2327,29 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B136" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B131" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="J4" s="9">
         <v>10</v>
@@ -2385,25 +2366,25 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>31</v>
+        <v>553</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="J5" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" s="7"/>
     </row>
@@ -2417,25 +2398,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>32</v>
+        <v>554</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="J6" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" s="9"/>
     </row>
@@ -2449,22 +2430,22 @@
         <v>4</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>294</v>
+        <v>540</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -2481,22 +2462,22 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="J8" s="9">
         <v>12</v>
@@ -2513,22 +2494,22 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -2541,24 +2522,26 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="12" t="s">
+        <v>3</v>
+      </c>
       <c r="D10" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
@@ -2575,22 +2558,22 @@
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
@@ -2607,22 +2590,22 @@
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="J12" s="9">
         <v>9</v>
@@ -2639,22 +2622,22 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="J13" s="7">
         <v>9</v>
@@ -2671,22 +2654,22 @@
         <v>3</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="J14" s="9">
         <v>2</v>
@@ -2703,22 +2686,22 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="J15" s="7">
         <v>3</v>
@@ -2735,22 +2718,22 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -2767,22 +2750,22 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -2799,22 +2782,22 @@
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="J18" s="9">
         <v>8</v>
@@ -2831,22 +2814,22 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="J19" s="7">
         <v>5</v>
@@ -2863,22 +2846,22 @@
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -2895,22 +2878,22 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="J21" s="7">
         <v>3</v>
@@ -2927,22 +2910,22 @@
         <v>2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="J22" s="9">
         <v>2</v>
@@ -2955,24 +2938,26 @@
         <f>ROW(B23) - ROW($B$2)</f>
         <v>21</v>
       </c>
-      <c r="C23" s="12"/>
+      <c r="C23" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="D23" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="J23" s="7">
         <v>3</v>
@@ -2989,22 +2974,22 @@
         <v>2</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
@@ -3017,26 +3002,26 @@
         <f>ROW(B25) - ROW($B$2)</f>
         <v>23</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
@@ -3053,22 +3038,22 @@
         <v>2</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>512</v>
+        <v>485</v>
       </c>
       <c r="J26" s="9">
         <v>2</v>
@@ -3081,24 +3066,26 @@
         <f>ROW(B27) - ROW($B$2)</f>
         <v>25</v>
       </c>
-      <c r="C27" s="12"/>
+      <c r="C27" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="D27" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
@@ -3111,24 +3098,26 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="13"/>
+      <c r="C28" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="D28" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
@@ -3141,26 +3130,26 @@
         <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>3</v>
+      <c r="C29" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="J29" s="7">
         <v>8</v>
@@ -3173,24 +3162,26 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="13"/>
+      <c r="C30" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="J30" s="9">
         <v>1</v>
@@ -3207,22 +3198,22 @@
         <v>3</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
@@ -3238,28 +3229,30 @@
       <c r="C32" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J32" s="15">
+      <c r="D32" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J32" s="14">
         <v>7</v>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3270,28 +3263,30 @@
       <c r="C33" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="I33" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J33" s="15">
-        <v>1</v>
-      </c>
-      <c r="K33" s="15"/>
+      <c r="D33" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="34" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3303,22 +3298,22 @@
         <v>5</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>374</v>
+        <v>541</v>
       </c>
       <c r="J34" s="9">
         <v>9</v>
@@ -3335,22 +3330,22 @@
         <v>6</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>375</v>
+        <v>437</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>541</v>
       </c>
       <c r="J35" s="7">
         <v>1</v>
@@ -3366,28 +3361,30 @@
       <c r="C36" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="I36" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J36" s="15">
-        <v>1</v>
-      </c>
-      <c r="K36" s="15"/>
+      <c r="D36" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J36" s="14">
+        <v>1</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
@@ -3399,22 +3396,22 @@
         <v>7</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>377</v>
+        <v>541</v>
       </c>
       <c r="J37" s="7">
         <v>2</v>
@@ -3427,24 +3424,26 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C38" s="13"/>
+      <c r="C38" s="13" t="s">
+        <v>557</v>
+      </c>
       <c r="D38" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F38" s="9">
-        <v>5027740891</v>
+        <v>187</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>540</v>
       </c>
       <c r="G38" s="10">
         <v>5027740891</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="I38" s="10">
-        <v>5027740891</v>
+        <v>439</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J38" s="9">
         <v>1</v>
@@ -3461,22 +3460,22 @@
         <v>8</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>302</v>
+        <v>540</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>302</v>
+        <v>541</v>
       </c>
       <c r="J39" s="7">
         <v>1</v>
@@ -3493,29 +3492,29 @@
         <v>9</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>303</v>
+        <v>189</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>540</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>303</v>
+        <v>441</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J40" s="9">
         <v>1</v>
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
@@ -3525,22 +3524,22 @@
         <v>10</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>304</v>
+        <v>540</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>304</v>
+        <v>541</v>
       </c>
       <c r="J41" s="7">
         <v>1</v>
@@ -3557,59 +3556,61 @@
         <v>11</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>305</v>
+        <v>191</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>540</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>305</v>
+        <v>442</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J42" s="9">
         <v>2</v>
       </c>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
-        <f>ROW(B43) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J43" s="15">
-        <v>1</v>
-      </c>
-      <c r="K43" s="17"/>
+      <c r="C43" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J43" s="14">
+        <v>1</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="44" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -3618,2108 +3619,2122 @@
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="I44" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J44" s="15">
-        <v>1</v>
-      </c>
-      <c r="K44" s="17"/>
-    </row>
-    <row r="45" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="J44" s="9">
+        <v>1</v>
+      </c>
+      <c r="K44" s="9"/>
+    </row>
+    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
-        <f>ROW(B45) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="I45" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J45" s="15">
-        <v>1</v>
-      </c>
-      <c r="K45" s="17"/>
-    </row>
-    <row r="46" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="J45" s="9">
+        <v>1</v>
+      </c>
+      <c r="K45" s="9"/>
+    </row>
+    <row r="46" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B46) - ROW($B$2)</f>
         <v>44</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="J46" s="9">
-        <v>1</v>
-      </c>
-      <c r="K46" s="9"/>
-    </row>
-    <row r="47" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="J46" s="7">
+        <v>3</v>
+      </c>
+      <c r="K46" s="7"/>
+    </row>
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f>ROW(B47) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>206</v>
+      <c r="D47" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>195</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="J47" s="7">
-        <v>1</v>
-      </c>
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="J47" s="9">
+        <v>1</v>
+      </c>
+      <c r="K47" s="9"/>
+    </row>
+    <row r="48" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B48) - ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="J48" s="9">
-        <v>1</v>
-      </c>
-      <c r="K48" s="9"/>
-    </row>
-    <row r="49" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="J48" s="7">
+        <v>1</v>
+      </c>
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f>ROW(B49) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="J49" s="7">
-        <v>3</v>
-      </c>
-      <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J49" s="14">
+        <v>1</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B50) - ROW($B$2)</f>
         <v>48</v>
       </c>
-      <c r="C50" s="13"/>
-      <c r="D50" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="J50" s="9">
-        <v>1</v>
-      </c>
-      <c r="K50" s="9"/>
+      <c r="C50" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J50" s="7">
+        <v>1</v>
+      </c>
+      <c r="K50" s="7"/>
     </row>
     <row r="51" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f>ROW(B51) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>474</v>
+      <c r="C51" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="J51" s="7">
-        <v>1</v>
-      </c>
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+      <c r="J51" s="9">
+        <v>5</v>
+      </c>
+      <c r="K51" s="9"/>
+    </row>
+    <row r="52" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B52) - ROW($B$2)</f>
         <v>50</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="I52" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J52" s="15">
-        <v>1</v>
-      </c>
-      <c r="K52" s="17"/>
-    </row>
-    <row r="53" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J52" s="7">
+        <v>2</v>
+      </c>
+      <c r="K52" s="7"/>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f>ROW(B53) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>475</v>
+      <c r="C53" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>450</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="J53" s="7">
-        <v>1</v>
-      </c>
-      <c r="K53" s="7"/>
+        <v>541</v>
+      </c>
+      <c r="J53" s="9">
+        <v>1</v>
+      </c>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B54) - ROW($B$2)</f>
         <v>52</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="J54" s="9">
-        <v>6</v>
-      </c>
-      <c r="K54" s="9"/>
-    </row>
-    <row r="55" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J54" s="7">
+        <v>1</v>
+      </c>
+      <c r="K54" s="7"/>
+    </row>
+    <row r="55" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f>ROW(B55) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>477</v>
+      <c r="C55" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>451</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="J55" s="7">
-        <v>2</v>
-      </c>
-      <c r="K55" s="7"/>
+        <v>541</v>
+      </c>
+      <c r="J55" s="9">
+        <v>1</v>
+      </c>
+      <c r="K55" s="9"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B56) - ROW($B$2)</f>
         <v>54</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="J56" s="9">
-        <v>1</v>
-      </c>
-      <c r="K56" s="9"/>
-    </row>
-    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J56" s="7">
+        <v>1</v>
+      </c>
+      <c r="K56" s="7"/>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
-        <f>ROW(B57) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>476</v>
+      <c r="D57" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>452</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="J57" s="7">
-        <v>1</v>
-      </c>
-      <c r="K57" s="7"/>
-    </row>
-    <row r="58" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+      <c r="J57" s="9">
+        <v>6</v>
+      </c>
+      <c r="K57" s="9"/>
+    </row>
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B58) - ROW($B$2)</f>
         <v>56</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="J58" s="9">
-        <v>1</v>
-      </c>
-      <c r="K58" s="9"/>
+      <c r="D58" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="J58" s="7">
+        <v>7</v>
+      </c>
+      <c r="K58" s="7"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
-        <f>ROW(B59) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="J59" s="7">
-        <v>1</v>
-      </c>
-      <c r="K59" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="J59" s="9">
+        <v>1</v>
+      </c>
+      <c r="K59" s="9"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B60) - ROW($B$2)</f>
         <v>58</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="J60" s="9">
-        <v>6</v>
-      </c>
-      <c r="K60" s="9"/>
+      <c r="D60" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="J60" s="7">
+        <v>1</v>
+      </c>
+      <c r="K60" s="7"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
-        <f>ROW(B61) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="J61" s="7">
-        <v>7</v>
-      </c>
-      <c r="K61" s="7"/>
+      <c r="C61" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="J61" s="9">
+        <v>1</v>
+      </c>
+      <c r="K61" s="9"/>
     </row>
     <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B62) - ROW($B$2)</f>
         <v>60</v>
       </c>
-      <c r="C62" s="13"/>
-      <c r="D62" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I62" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="J62" s="9">
-        <v>1</v>
-      </c>
-      <c r="K62" s="9"/>
+      <c r="C62" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="J62" s="7">
+        <v>1</v>
+      </c>
+      <c r="K62" s="7"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
-        <f>ROW(B63) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="J63" s="7">
-        <v>1</v>
-      </c>
-      <c r="K63" s="7"/>
+      <c r="C63" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="J63" s="9">
+        <v>1</v>
+      </c>
+      <c r="K63" s="9"/>
     </row>
     <row r="64" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B64) - ROW($B$2)</f>
         <v>62</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I64" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="J64" s="9">
-        <v>1</v>
-      </c>
-      <c r="K64" s="9"/>
+      <c r="C64" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="J64" s="7">
+        <v>1</v>
+      </c>
+      <c r="K64" s="7"/>
     </row>
     <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
-        <f>ROW(B65) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="J65" s="7">
-        <v>1</v>
-      </c>
-      <c r="K65" s="7"/>
+      <c r="C65" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="J65" s="9">
+        <v>1</v>
+      </c>
+      <c r="K65" s="9"/>
     </row>
     <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B66) - ROW($B$2)</f>
         <v>64</v>
       </c>
-      <c r="C66" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I66" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="J66" s="9">
-        <v>1</v>
-      </c>
-      <c r="K66" s="9"/>
+      <c r="C66" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="J66" s="7">
+        <v>1</v>
+      </c>
+      <c r="K66" s="7"/>
     </row>
     <row r="67" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
-        <f>ROW(B67) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I67" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="J67" s="7">
-        <v>1</v>
-      </c>
-      <c r="K67" s="7"/>
+      <c r="C67" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="J67" s="9">
+        <v>1</v>
+      </c>
+      <c r="K67" s="9"/>
     </row>
     <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B68) - ROW($B$2)</f>
         <v>66</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I68" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="J68" s="9">
-        <v>1</v>
-      </c>
-      <c r="K68" s="9"/>
+      <c r="C68" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="J68" s="7">
+        <v>1</v>
+      </c>
+      <c r="K68" s="7"/>
     </row>
     <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
-        <f>ROW(B69) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="J69" s="7">
-        <v>1</v>
-      </c>
-      <c r="K69" s="7"/>
+      <c r="C69" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="J69" s="9">
+        <v>6</v>
+      </c>
+      <c r="K69" s="9"/>
     </row>
     <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B70) - ROW($B$2)</f>
         <v>68</v>
       </c>
-      <c r="C70" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="J70" s="9">
-        <v>1</v>
-      </c>
-      <c r="K70" s="9"/>
-    </row>
-    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="J70" s="7">
+        <v>1</v>
+      </c>
+      <c r="K70" s="7"/>
+    </row>
+    <row r="71" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
-        <f>ROW(B71) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C71" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="J71" s="7">
-        <v>1</v>
-      </c>
-      <c r="K71" s="7"/>
+      <c r="C71" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="J71" s="9">
+        <v>19</v>
+      </c>
+      <c r="K71" s="9"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B72) - ROW($B$2)</f>
         <v>70</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I72" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="J72" s="9">
-        <v>7</v>
-      </c>
-      <c r="K72" s="9"/>
+      <c r="C72" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="J72" s="7">
+        <v>2</v>
+      </c>
+      <c r="K72" s="7"/>
     </row>
     <row r="73" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f>ROW(B73) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="J73" s="7">
-        <v>1</v>
-      </c>
-      <c r="K73" s="7"/>
-    </row>
-    <row r="74" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="J73" s="9">
+        <v>1</v>
+      </c>
+      <c r="K73" s="9"/>
+    </row>
+    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B74) - ROW($B$2)</f>
         <v>72</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I74" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="J74" s="9">
-        <v>19</v>
-      </c>
-      <c r="K74" s="9"/>
-    </row>
-    <row r="75" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="J74" s="7">
+        <v>1</v>
+      </c>
+      <c r="K74" s="7"/>
+    </row>
+    <row r="75" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
-        <f>ROW(B75) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="J75" s="7">
-        <v>2</v>
-      </c>
-      <c r="K75" s="7"/>
+      <c r="C75" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="J75" s="9">
+        <v>10</v>
+      </c>
+      <c r="K75" s="9"/>
     </row>
     <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B76) - ROW($B$2)</f>
         <v>74</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="H76" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>537</v>
-      </c>
-      <c r="J76" s="9">
-        <v>1</v>
-      </c>
-      <c r="K76" s="9"/>
+      <c r="C76" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="J76" s="7">
+        <v>1</v>
+      </c>
+      <c r="K76" s="7"/>
     </row>
     <row r="77" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
-        <f>ROW(B77) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C77" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="J77" s="7">
-        <v>1</v>
-      </c>
-      <c r="K77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="J77" s="9">
+        <v>1</v>
+      </c>
+      <c r="K77" s="9"/>
+    </row>
+    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B78) - ROW($B$2)</f>
         <v>76</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I78" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="J78" s="9">
-        <v>10</v>
-      </c>
-      <c r="K78" s="9"/>
+      <c r="C78" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="J78" s="7">
+        <v>1</v>
+      </c>
+      <c r="K78" s="7"/>
     </row>
     <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
-        <f>ROW(B79) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="C79" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="J79" s="7">
-        <v>1</v>
-      </c>
-      <c r="K79" s="7"/>
+      <c r="C79" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="J79" s="9">
+        <v>1</v>
+      </c>
+      <c r="K79" s="9"/>
     </row>
     <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B80) - ROW($B$2)</f>
         <v>78</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I80" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="J80" s="9">
-        <v>1</v>
-      </c>
-      <c r="K80" s="9"/>
+      <c r="C80" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J80" s="7">
+        <v>1</v>
+      </c>
+      <c r="K80" s="7"/>
     </row>
     <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
-        <f>ROW(B81) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="C81" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J81" s="7">
-        <v>1</v>
-      </c>
-      <c r="K81" s="7"/>
+      <c r="C81" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="J81" s="9">
+        <v>8</v>
+      </c>
+      <c r="K81" s="9"/>
     </row>
     <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B82) - ROW($B$2)</f>
         <v>80</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>542</v>
-      </c>
-      <c r="J82" s="9">
-        <v>1</v>
-      </c>
-      <c r="K82" s="9"/>
+      <c r="C82" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="J82" s="7">
+        <v>4</v>
+      </c>
+      <c r="K82" s="7"/>
     </row>
     <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
-        <f>ROW(B83) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C83" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="J83" s="7">
-        <v>1</v>
-      </c>
-      <c r="K83" s="7"/>
+      <c r="C83" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="J83" s="9">
+        <v>5</v>
+      </c>
+      <c r="K83" s="9"/>
     </row>
     <row r="84" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B84) - ROW($B$2)</f>
         <v>82</v>
       </c>
-      <c r="C84" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I84" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="J84" s="9">
-        <v>8</v>
-      </c>
-      <c r="K84" s="9"/>
+      <c r="C84" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="J84" s="7">
+        <v>1</v>
+      </c>
+      <c r="K84" s="7"/>
     </row>
     <row r="85" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
-        <f>ROW(B85) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>414</v>
+        <v>19</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>538</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="J85" s="7">
-        <v>4</v>
-      </c>
-      <c r="K85" s="7"/>
+        <v>434</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="J85" s="9">
+        <v>2</v>
+      </c>
+      <c r="K85" s="9"/>
     </row>
     <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B86) - ROW($B$2)</f>
         <v>84</v>
       </c>
-      <c r="C86" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I86" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="J86" s="9">
-        <v>5</v>
-      </c>
-      <c r="K86" s="9"/>
+      <c r="C86" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="J86" s="7">
+        <v>1</v>
+      </c>
+      <c r="K86" s="7"/>
     </row>
     <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f>ROW(B87) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I87" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="J87" s="7">
-        <v>1</v>
-      </c>
-      <c r="K87" s="7"/>
+      <c r="C87" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="J87" s="9">
+        <v>1</v>
+      </c>
+      <c r="K87" s="9"/>
     </row>
     <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B88) - ROW($B$2)</f>
         <v>86</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>569</v>
+        <v>19</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>395</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I88" s="10" t="s">
-        <v>546</v>
-      </c>
-      <c r="J88" s="9">
-        <v>2</v>
-      </c>
-      <c r="K88" s="9"/>
+        <v>434</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="J88" s="7">
+        <v>1</v>
+      </c>
+      <c r="K88" s="7"/>
     </row>
     <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
-        <f>ROW(B89) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="J89" s="7">
-        <v>1</v>
-      </c>
-      <c r="K89" s="7"/>
+      <c r="C89" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="J89" s="9">
+        <v>1</v>
+      </c>
+      <c r="K89" s="9"/>
     </row>
     <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B90) - ROW($B$2)</f>
         <v>88</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I90" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="J90" s="9">
-        <v>1</v>
-      </c>
-      <c r="K90" s="9"/>
+      <c r="C90" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="J90" s="7">
+        <v>1</v>
+      </c>
+      <c r="K90" s="7"/>
     </row>
     <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
-        <f>ROW(B91) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C91" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="J91" s="7">
-        <v>1</v>
-      </c>
-      <c r="K91" s="7"/>
+      <c r="C91" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I91" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="J91" s="9">
+        <v>1</v>
+      </c>
+      <c r="K91" s="9"/>
     </row>
     <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B92) - ROW($B$2)</f>
         <v>90</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I92" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="J92" s="9">
-        <v>1</v>
-      </c>
-      <c r="K92" s="9"/>
+      <c r="C92" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="J92" s="7">
+        <v>3</v>
+      </c>
+      <c r="K92" s="7"/>
     </row>
     <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="11">
-        <f>ROW(B93) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C93" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="J93" s="7">
-        <v>1</v>
-      </c>
-      <c r="K93" s="7"/>
+      <c r="C93" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I93" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="J93" s="9">
+        <v>6</v>
+      </c>
+      <c r="K93" s="9"/>
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B94) - ROW($B$2)</f>
         <v>92</v>
       </c>
-      <c r="C94" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I94" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="J94" s="9">
-        <v>1</v>
-      </c>
-      <c r="K94" s="9"/>
+      <c r="C94" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1</v>
+      </c>
+      <c r="K94" s="7"/>
     </row>
     <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
-        <f>ROW(B95) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="J95" s="7">
-        <v>3</v>
-      </c>
-      <c r="K95" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J95" s="9">
+        <v>1</v>
+      </c>
+      <c r="K95" s="9"/>
     </row>
     <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B96) - ROW($B$2)</f>
         <v>94</v>
       </c>
-      <c r="C96" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I96" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="J96" s="9">
-        <v>6</v>
-      </c>
-      <c r="K96" s="9"/>
+      <c r="C96" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J96" s="7">
+        <v>1</v>
+      </c>
+      <c r="K96" s="7"/>
     </row>
     <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="11">
-        <f>ROW(B97) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="C97" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="J97" s="7">
-        <v>1</v>
-      </c>
-      <c r="K97" s="7"/>
+      <c r="C97" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="J97" s="9">
+        <v>2</v>
+      </c>
+      <c r="K97" s="9"/>
     </row>
     <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B98) - ROW($B$2)</f>
         <v>96</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I98" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="J98" s="9">
-        <v>1</v>
-      </c>
-      <c r="K98" s="9"/>
-    </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F98" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J98" s="14">
+        <v>2</v>
+      </c>
+      <c r="K98" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
-        <f>ROW(B99) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="C99" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="J99" s="7">
-        <v>1</v>
-      </c>
-      <c r="K99" s="7"/>
+      <c r="C99" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="J99" s="9">
+        <v>1</v>
+      </c>
+      <c r="K99" s="9"/>
     </row>
     <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B100) - ROW($B$2)</f>
         <v>98</v>
       </c>
-      <c r="C100" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="H100" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I100" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="J100" s="9">
-        <v>2</v>
-      </c>
-      <c r="K100" s="9"/>
+      <c r="C100" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="J100" s="7">
+        <v>1</v>
+      </c>
+      <c r="K100" s="7"/>
     </row>
     <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
-        <f>ROW(B101) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="C101" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D101" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E101" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="F101" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="G101" s="16" t="s">
+      <c r="C101" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G101" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="H101" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="I101" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J101" s="15">
-        <v>2</v>
-      </c>
-      <c r="K101" s="17" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H101" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="J101" s="9">
+        <v>1</v>
+      </c>
+      <c r="K101" s="9"/>
+    </row>
+    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B102) - ROW($B$2)</f>
         <v>100</v>
       </c>
-      <c r="C102" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I102" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="J102" s="9">
-        <v>1</v>
-      </c>
-      <c r="K102" s="9"/>
+      <c r="C102" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="J102" s="7">
+        <v>1</v>
+      </c>
+      <c r="K102" s="7"/>
     </row>
     <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="11">
-        <f>ROW(B103) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="C103" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="J103" s="7">
-        <v>1</v>
-      </c>
-      <c r="K103" s="7"/>
+      <c r="C103" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I103" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J103" s="14">
+        <v>1</v>
+      </c>
+      <c r="K103" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B104) - ROW($B$2)</f>
         <v>102</v>
       </c>
-      <c r="C104" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I104" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="J104" s="9">
-        <v>1</v>
-      </c>
-      <c r="K104" s="9"/>
+      <c r="C104" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="J104" s="7">
+        <v>1</v>
+      </c>
+      <c r="K104" s="7"/>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="11">
-        <f>ROW(B105) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="J105" s="7">
-        <v>1</v>
-      </c>
-      <c r="K105" s="7"/>
+      <c r="C105" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G105" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J105" s="14">
+        <v>1</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B106) - ROW($B$2)</f>
         <v>104</v>
       </c>
-      <c r="C106" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E106" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="F106" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="G106" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="H106" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="I106" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J106" s="15">
-        <v>1</v>
-      </c>
-      <c r="K106" s="17"/>
+      <c r="C106" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="J106" s="7">
+        <v>4</v>
+      </c>
+      <c r="K106" s="7"/>
     </row>
     <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
-        <f>ROW(B107) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="C107" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="J107" s="7">
-        <v>1</v>
-      </c>
-      <c r="K107" s="7"/>
+      <c r="C107" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="J107" s="9">
+        <v>1</v>
+      </c>
+      <c r="K107" s="9"/>
     </row>
     <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B108) - ROW($B$2)</f>
         <v>106</v>
       </c>
-      <c r="C108" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E108" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="F108" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="G108" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="H108" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="I108" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J108" s="15">
-        <v>1</v>
-      </c>
-      <c r="K108" s="17"/>
+      <c r="C108" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G108" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="H108" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J108" s="14">
+        <v>1</v>
+      </c>
+      <c r="K108" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="11">
-        <f>ROW(B109) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="C109" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G109" s="8" t="s">
+      <c r="C109" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="G109" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="H109" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="H109" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="J109" s="7">
-        <v>4</v>
-      </c>
-      <c r="K109" s="7"/>
+      <c r="I109" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="J109" s="14">
+        <v>2</v>
+      </c>
+      <c r="K109" s="16" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
@@ -5728,32 +5743,32 @@
         <v>108</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J110" s="9">
         <v>1</v>
       </c>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="11">
         <f>ROW(B111) - ROW($B$2)</f>
@@ -5762,30 +5777,30 @@
       <c r="C111" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D111" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E111" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="F111" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="G111" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="H111" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="I111" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J111" s="15">
-        <v>1</v>
-      </c>
-      <c r="K111" s="17"/>
-    </row>
-    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D111" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J111" s="7">
+        <v>1</v>
+      </c>
+      <c r="K111" s="7"/>
+    </row>
+    <row r="112" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="11">
         <f t="shared" si="0"/>
@@ -5794,92 +5809,94 @@
       <c r="C112" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D112" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E112" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="F112" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="G112" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="H112" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="I112" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J112" s="15">
-        <v>2</v>
-      </c>
-      <c r="K112" s="17"/>
-    </row>
-    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D112" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J112" s="9">
+        <v>1</v>
+      </c>
+      <c r="K112" s="9"/>
+    </row>
+    <row r="113" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
         <f>ROW(B113) - ROW($B$2)</f>
         <v>111</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>321</v>
+        <v>540</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>436</v>
+        <v>305</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="J113" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K113" s="7"/>
     </row>
-    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="C114" s="13"/>
+      <c r="C114" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="D114" s="9" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I114" s="10" t="s">
-        <v>563</v>
+        <v>455</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J114" s="9">
         <v>1</v>
       </c>
       <c r="K114" s="9"/>
     </row>
-    <row r="115" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="11">
         <f>ROW(B115) - ROW($B$2)</f>
@@ -5889,118 +5906,118 @@
         <v>22</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>323</v>
+        <v>414</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>323</v>
+        <v>541</v>
       </c>
       <c r="J115" s="7">
         <v>1</v>
       </c>
       <c r="K115" s="7"/>
     </row>
-    <row r="116" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="11">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>324</v>
+        <v>457</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J116" s="9">
         <v>1</v>
       </c>
       <c r="K116" s="9"/>
     </row>
-    <row r="117" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="11">
         <f>ROW(B117) - ROW($B$2)</f>
         <v>115</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>325</v>
+        <v>541</v>
       </c>
       <c r="J117" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K117" s="7"/>
     </row>
-    <row r="118" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="11">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="I118" s="10" t="s">
-        <v>438</v>
+        <v>459</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J118" s="9">
         <v>1</v>
@@ -6014,25 +6031,25 @@
         <v>117</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>439</v>
+        <v>541</v>
       </c>
       <c r="J119" s="7">
         <v>1</v>
@@ -6046,57 +6063,57 @@
         <v>118</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="I120" s="10" t="s">
-        <v>440</v>
+        <v>459</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J120" s="9">
         <v>1</v>
       </c>
       <c r="K120" s="9"/>
     </row>
-    <row r="121" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="11">
         <f>ROW(B121) - ROW($B$2)</f>
         <v>119</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>441</v>
+        <v>541</v>
       </c>
       <c r="J121" s="7">
         <v>1</v>
@@ -6110,25 +6127,25 @@
         <v>120</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="G122" s="10" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="I122" s="10" t="s">
-        <v>442</v>
+        <v>460</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J122" s="9">
         <v>1</v>
@@ -6142,89 +6159,89 @@
         <v>121</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>443</v>
+        <v>541</v>
       </c>
       <c r="J123" s="7">
         <v>1</v>
       </c>
       <c r="K123" s="7"/>
     </row>
-    <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="11">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="G124" s="10" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="I124" s="10" t="s">
-        <v>444</v>
+        <v>461</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J124" s="9">
         <v>1</v>
       </c>
       <c r="K124" s="9"/>
     </row>
-    <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="11">
         <f>ROW(B125) - ROW($B$2)</f>
         <v>123</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>445</v>
+        <v>541</v>
       </c>
       <c r="J125" s="7">
         <v>1</v>
@@ -6238,350 +6255,316 @@
         <v>124</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="F126" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="I126" s="10" t="s">
-        <v>446</v>
+        <v>459</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J126" s="9">
         <v>1</v>
       </c>
       <c r="K126" s="9"/>
     </row>
-    <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="11">
         <f>ROW(B127) - ROW($B$2)</f>
         <v>125</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>334</v>
+        <v>540</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>447</v>
+        <v>318</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>447</v>
+        <v>541</v>
       </c>
       <c r="J127" s="7">
         <v>1</v>
       </c>
       <c r="K127" s="7"/>
     </row>
-    <row r="128" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="11">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="I128" s="10" t="s">
-        <v>448</v>
+        <v>459</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="J128" s="9">
         <v>1</v>
       </c>
       <c r="K128" s="9"/>
     </row>
-    <row r="129" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="11">
-        <f>ROW(B129) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="I129" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="J129" s="7">
-        <v>1</v>
-      </c>
-      <c r="K129" s="7"/>
+      <c r="C129" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="I129" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="J129" s="9">
+        <v>1</v>
+      </c>
+      <c r="K129" s="9"/>
     </row>
     <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B130) - ROW($B$2)</f>
         <v>128</v>
       </c>
-      <c r="C130" s="13" t="s">
+      <c r="C130" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D130" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="G130" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="H130" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="I130" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="J130" s="9">
-        <v>1</v>
-      </c>
-      <c r="K130" s="9"/>
-    </row>
-    <row r="131" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D130" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="J130" s="7">
+        <v>2</v>
+      </c>
+      <c r="K130" s="7"/>
+    </row>
+    <row r="131" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="11">
-        <f>ROW(B131) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="J131" s="7">
-        <v>1</v>
-      </c>
-      <c r="K131" s="7"/>
-    </row>
-    <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="1"/>
+      <c r="C131" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="J131" s="9">
+        <v>1</v>
+      </c>
+      <c r="K131" s="9"/>
+    </row>
+    <row r="132" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B132" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B132) - ROW($B$2)</f>
         <v>130</v>
       </c>
-      <c r="C132" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D132" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="F132" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="I132" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="J132" s="9">
-        <v>1</v>
-      </c>
-      <c r="K132" s="9"/>
-    </row>
-    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="1"/>
+      <c r="C132" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J132" s="7">
+        <v>2</v>
+      </c>
+      <c r="K132" s="7"/>
+    </row>
+    <row r="133" spans="1:11" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B133" s="11">
         <f>ROW(B133) - ROW($B$2)</f>
         <v>131</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>24</v>
+        <v>542</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>159</v>
+        <v>541</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>340</v>
+        <v>547</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>452</v>
+        <v>546</v>
       </c>
       <c r="H133" s="7" t="s">
-        <v>484</v>
+        <v>548</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>452</v>
+        <v>541</v>
       </c>
       <c r="J133" s="7">
         <v>1</v>
       </c>
-      <c r="K133" s="7"/>
+      <c r="K133" s="17" t="s">
+        <v>549</v>
+      </c>
     </row>
     <row r="134" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="1"/>
       <c r="B134" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B134:B135" si="1">ROW(B134) - ROW($B$2)</f>
         <v>132</v>
       </c>
-      <c r="C134" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D134" s="9" t="s">
-        <v>160</v>
+      <c r="C134" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>541</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>288</v>
+        <v>552</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>341</v>
+        <v>540</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>453</v>
+        <v>550</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>490</v>
+        <v>551</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="J134" s="9">
         <v>1</v>
       </c>
       <c r="K134" s="9"/>
     </row>
-    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="1"/>
+    <row r="135" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B135" s="11">
-        <f>ROW(B135) - ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>133</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>26</v>
+        <v>542</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="I135" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="J135" s="7">
+        <v>541</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="I135" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="J135" s="9">
         <v>2</v>
       </c>
-      <c r="K135" s="7"/>
-    </row>
-    <row r="136" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="1"/>
-      <c r="B136" s="11">
-        <f t="shared" si="0"/>
-        <v>134</v>
-      </c>
-      <c r="C136" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="F136" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="I136" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="J136" s="9">
-        <v>1</v>
-      </c>
-      <c r="K136" s="9"/>
+      <c r="K135" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="565">
   <si>
     <t>#</t>
   </si>
@@ -1702,13 +1702,25 @@
   </si>
   <si>
     <t>MyAntenna</t>
+  </si>
+  <si>
+    <t>FPC FFC Flexible Flat Cable Extension Board PCB Pitch 0.5 mm (40 Pin) Connector</t>
+  </si>
+  <si>
+    <t>CA-2660</t>
+  </si>
+  <si>
+    <t>RZCONNE</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1776,6 +1788,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1797,7 +1824,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1888,11 +1915,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1944,8 +1987,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2231,8 +2278,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K135"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K136"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
@@ -2246,7 +2293,7 @@
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2259,7 +2306,7 @@
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2292,7 +2339,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -2324,7 +2371,7 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
         <f t="shared" ref="B4:B131" si="0">ROW(B4) - ROW($B$2)</f>
@@ -2356,7 +2403,7 @@
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="24.75" thickBot="1">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -2388,7 +2435,7 @@
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="48.75" thickBot="1">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -2420,7 +2467,7 @@
       </c>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15.75" thickBot="1">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -2452,7 +2499,7 @@
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="24.75" thickBot="1">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -2484,7 +2531,7 @@
       </c>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -2516,7 +2563,7 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -2548,7 +2595,7 @@
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15.75" thickBot="1">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -2580,7 +2627,7 @@
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="24.75" thickBot="1">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -2612,7 +2659,7 @@
       </c>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
@@ -2644,7 +2691,7 @@
       </c>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="15.75" thickBot="1">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -2676,7 +2723,7 @@
       </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="15.75" thickBot="1">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
@@ -2708,7 +2755,7 @@
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -2740,7 +2787,7 @@
       </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
@@ -2772,7 +2819,7 @@
       </c>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15.75" thickBot="1">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <f t="shared" si="0"/>
@@ -2804,7 +2851,7 @@
       </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -2836,7 +2883,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
         <f t="shared" si="0"/>
@@ -2868,7 +2915,7 @@
       </c>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15.75" thickBot="1">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
@@ -2900,7 +2947,7 @@
       </c>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15.75" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
         <f t="shared" si="0"/>
@@ -2932,7 +2979,7 @@
       </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15.75" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
@@ -2964,7 +3011,7 @@
       </c>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15.75" thickBot="1">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
@@ -2996,7 +3043,7 @@
       </c>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15.75" thickBot="1">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
         <f>ROW(B25) - ROW($B$2)</f>
@@ -3028,7 +3075,7 @@
       </c>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15.75" thickBot="1">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
@@ -3060,7 +3107,7 @@
       </c>
       <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="15.75" thickBot="1">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f>ROW(B27) - ROW($B$2)</f>
@@ -3092,7 +3139,7 @@
       </c>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15.75" thickBot="1">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
@@ -3124,7 +3171,7 @@
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15.75" thickBot="1">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
@@ -3156,7 +3203,7 @@
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15.75" thickBot="1">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
@@ -3188,7 +3235,7 @@
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15.75" thickBot="1">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
@@ -3220,7 +3267,7 @@
       </c>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15.75" thickBot="1">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f t="shared" si="0"/>
@@ -3254,7 +3301,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="15.75" thickBot="1">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f>ROW(B33) - ROW($B$2)</f>
@@ -3288,7 +3335,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="36.75" thickBot="1">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f t="shared" si="0"/>
@@ -3320,7 +3367,7 @@
       </c>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="24.75" thickBot="1">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f>ROW(B35) - ROW($B$2)</f>
@@ -3352,7 +3399,7 @@
       </c>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="15.75" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
@@ -3386,7 +3433,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f>ROW(B37) - ROW($B$2)</f>
@@ -3418,7 +3465,7 @@
       </c>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="36.75" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
@@ -3450,7 +3497,7 @@
       </c>
       <c r="K38" s="9"/>
     </row>
-    <row r="39" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="48.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
@@ -3482,7 +3529,7 @@
       </c>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="24.75" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
@@ -3514,7 +3561,7 @@
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="15.75" thickBot="1">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
@@ -3546,7 +3593,7 @@
       </c>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="26.25" thickBot="1">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
@@ -3578,7 +3625,7 @@
       </c>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="26.25" thickBot="1">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
@@ -3612,7 +3659,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="26.25" thickBot="1">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
@@ -3644,7 +3691,7 @@
       </c>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="15.75" thickBot="1">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
@@ -3676,7 +3723,7 @@
       </c>
       <c r="K45" s="9"/>
     </row>
-    <row r="46" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="24.75" thickBot="1">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f>ROW(B46) - ROW($B$2)</f>
@@ -3708,7 +3755,7 @@
       </c>
       <c r="K46" s="7"/>
     </row>
-    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="15.75" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f t="shared" si="0"/>
@@ -3740,7 +3787,7 @@
       </c>
       <c r="K47" s="9"/>
     </row>
-    <row r="48" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="24.75" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f>ROW(B48) - ROW($B$2)</f>
@@ -3772,7 +3819,7 @@
       </c>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="15.75" thickBot="1">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f t="shared" si="0"/>
@@ -3806,7 +3853,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="24.75" thickBot="1">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f>ROW(B50) - ROW($B$2)</f>
@@ -3838,7 +3885,7 @@
       </c>
       <c r="K50" s="7"/>
     </row>
-    <row r="51" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="24.75" thickBot="1">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f t="shared" si="0"/>
@@ -3870,7 +3917,7 @@
       </c>
       <c r="K51" s="9"/>
     </row>
-    <row r="52" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="24.75" thickBot="1">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f>ROW(B52) - ROW($B$2)</f>
@@ -3902,7 +3949,7 @@
       </c>
       <c r="K52" s="7"/>
     </row>
-    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="15.75" thickBot="1">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f t="shared" si="0"/>
@@ -3934,7 +3981,7 @@
       </c>
       <c r="K53" s="9"/>
     </row>
-    <row r="54" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="24.75" thickBot="1">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f>ROW(B54) - ROW($B$2)</f>
@@ -3966,7 +4013,7 @@
       </c>
       <c r="K54" s="7"/>
     </row>
-    <row r="55" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="36.75" thickBot="1">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f t="shared" si="0"/>
@@ -3998,7 +4045,7 @@
       </c>
       <c r="K55" s="9"/>
     </row>
-    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="15.75" thickBot="1">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f>ROW(B56) - ROW($B$2)</f>
@@ -4030,7 +4077,7 @@
       </c>
       <c r="K56" s="7"/>
     </row>
-    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="15.75" thickBot="1">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f t="shared" si="0"/>
@@ -4062,7 +4109,7 @@
       </c>
       <c r="K57" s="9"/>
     </row>
-    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="15.75" thickBot="1">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f>ROW(B58) - ROW($B$2)</f>
@@ -4094,7 +4141,7 @@
       </c>
       <c r="K58" s="7"/>
     </row>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="15.75" thickBot="1">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f t="shared" si="0"/>
@@ -4126,7 +4173,7 @@
       </c>
       <c r="K59" s="9"/>
     </row>
-    <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="15.75" thickBot="1">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f>ROW(B60) - ROW($B$2)</f>
@@ -4158,7 +4205,7 @@
       </c>
       <c r="K60" s="7"/>
     </row>
-    <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="15.75" thickBot="1">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f t="shared" si="0"/>
@@ -4190,7 +4237,7 @@
       </c>
       <c r="K61" s="9"/>
     </row>
-    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="15.75" thickBot="1">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f>ROW(B62) - ROW($B$2)</f>
@@ -4222,7 +4269,7 @@
       </c>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="15.75" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f t="shared" si="0"/>
@@ -4254,7 +4301,7 @@
       </c>
       <c r="K63" s="9"/>
     </row>
-    <row r="64" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="15.75" thickBot="1">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f>ROW(B64) - ROW($B$2)</f>
@@ -4286,7 +4333,7 @@
       </c>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="15.75" thickBot="1">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f t="shared" si="0"/>
@@ -4318,7 +4365,7 @@
       </c>
       <c r="K65" s="9"/>
     </row>
-    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="15.75" thickBot="1">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f>ROW(B66) - ROW($B$2)</f>
@@ -4350,7 +4397,7 @@
       </c>
       <c r="K66" s="7"/>
     </row>
-    <row r="67" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="15.75" thickBot="1">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="0"/>
@@ -4382,7 +4429,7 @@
       </c>
       <c r="K67" s="9"/>
     </row>
-    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="15.75" thickBot="1">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f>ROW(B68) - ROW($B$2)</f>
@@ -4414,7 +4461,7 @@
       </c>
       <c r="K68" s="7"/>
     </row>
-    <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="15.75" thickBot="1">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="0"/>
@@ -4446,7 +4493,7 @@
       </c>
       <c r="K69" s="9"/>
     </row>
-    <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="15.75" thickBot="1">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f>ROW(B70) - ROW($B$2)</f>
@@ -4478,7 +4525,7 @@
       </c>
       <c r="K70" s="7"/>
     </row>
-    <row r="71" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" ht="36.75" thickBot="1">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f t="shared" si="0"/>
@@ -4510,7 +4557,7 @@
       </c>
       <c r="K71" s="9"/>
     </row>
-    <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="15.75" thickBot="1">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f>ROW(B72) - ROW($B$2)</f>
@@ -4542,7 +4589,7 @@
       </c>
       <c r="K72" s="7"/>
     </row>
-    <row r="73" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" ht="15.75" thickBot="1">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f t="shared" si="0"/>
@@ -4574,7 +4621,7 @@
       </c>
       <c r="K73" s="9"/>
     </row>
-    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="15.75" thickBot="1">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f>ROW(B74) - ROW($B$2)</f>
@@ -4606,7 +4653,7 @@
       </c>
       <c r="K74" s="7"/>
     </row>
-    <row r="75" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" ht="24.75" thickBot="1">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f t="shared" si="0"/>
@@ -4638,7 +4685,7 @@
       </c>
       <c r="K75" s="9"/>
     </row>
-    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="15.75" thickBot="1">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f>ROW(B76) - ROW($B$2)</f>
@@ -4670,7 +4717,7 @@
       </c>
       <c r="K76" s="7"/>
     </row>
-    <row r="77" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="15.75" thickBot="1">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f t="shared" si="0"/>
@@ -4702,7 +4749,7 @@
       </c>
       <c r="K77" s="9"/>
     </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="15.75" thickBot="1">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f>ROW(B78) - ROW($B$2)</f>
@@ -4734,7 +4781,7 @@
       </c>
       <c r="K78" s="7"/>
     </row>
-    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="15.75" thickBot="1">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f t="shared" si="0"/>
@@ -4766,7 +4813,7 @@
       </c>
       <c r="K79" s="9"/>
     </row>
-    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="15.75" thickBot="1">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f>ROW(B80) - ROW($B$2)</f>
@@ -4798,7 +4845,7 @@
       </c>
       <c r="K80" s="7"/>
     </row>
-    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="15.75" thickBot="1">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="0"/>
@@ -4830,7 +4877,7 @@
       </c>
       <c r="K81" s="9"/>
     </row>
-    <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="15.75" thickBot="1">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f>ROW(B82) - ROW($B$2)</f>
@@ -4862,7 +4909,7 @@
       </c>
       <c r="K82" s="7"/>
     </row>
-    <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="15.75" thickBot="1">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f t="shared" si="0"/>
@@ -4894,7 +4941,7 @@
       </c>
       <c r="K83" s="9"/>
     </row>
-    <row r="84" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="15.75" thickBot="1">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f>ROW(B84) - ROW($B$2)</f>
@@ -4926,7 +4973,7 @@
       </c>
       <c r="K84" s="7"/>
     </row>
-    <row r="85" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="15.75" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f t="shared" si="0"/>
@@ -4958,7 +5005,7 @@
       </c>
       <c r="K85" s="9"/>
     </row>
-    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="15.75" thickBot="1">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f>ROW(B86) - ROW($B$2)</f>
@@ -4990,7 +5037,7 @@
       </c>
       <c r="K86" s="7"/>
     </row>
-    <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="15.75" thickBot="1">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
         <f t="shared" si="0"/>
@@ -5022,7 +5069,7 @@
       </c>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="15.75" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f>ROW(B88) - ROW($B$2)</f>
@@ -5054,7 +5101,7 @@
       </c>
       <c r="K88" s="7"/>
     </row>
-    <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="15.75" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
         <f t="shared" si="0"/>
@@ -5086,7 +5133,7 @@
       </c>
       <c r="K89" s="9"/>
     </row>
-    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="15.75" thickBot="1">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f>ROW(B90) - ROW($B$2)</f>
@@ -5118,7 +5165,7 @@
       </c>
       <c r="K90" s="7"/>
     </row>
-    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="15.75" thickBot="1">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f t="shared" si="0"/>
@@ -5150,7 +5197,7 @@
       </c>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="15.75" thickBot="1">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f>ROW(B92) - ROW($B$2)</f>
@@ -5182,7 +5229,7 @@
       </c>
       <c r="K92" s="7"/>
     </row>
-    <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="15.75" thickBot="1">
       <c r="A93" s="1"/>
       <c r="B93" s="11">
         <f t="shared" si="0"/>
@@ -5214,7 +5261,7 @@
       </c>
       <c r="K93" s="9"/>
     </row>
-    <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" ht="15.75" thickBot="1">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
         <f>ROW(B94) - ROW($B$2)</f>
@@ -5246,7 +5293,7 @@
       </c>
       <c r="K94" s="7"/>
     </row>
-    <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" ht="15.75" thickBot="1">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
         <f t="shared" si="0"/>
@@ -5278,7 +5325,7 @@
       </c>
       <c r="K95" s="9"/>
     </row>
-    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="15.75" thickBot="1">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f>ROW(B96) - ROW($B$2)</f>
@@ -5310,7 +5357,7 @@
       </c>
       <c r="K96" s="7"/>
     </row>
-    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="15.75" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="11">
         <f t="shared" si="0"/>
@@ -5342,7 +5389,7 @@
       </c>
       <c r="K97" s="9"/>
     </row>
-    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="15.75" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
         <f>ROW(B98) - ROW($B$2)</f>
@@ -5376,7 +5423,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="36.75" thickBot="1">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f t="shared" si="0"/>
@@ -5408,7 +5455,7 @@
       </c>
       <c r="K99" s="9"/>
     </row>
-    <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="15.75" thickBot="1">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
         <f>ROW(B100) - ROW($B$2)</f>
@@ -5440,7 +5487,7 @@
       </c>
       <c r="K100" s="7"/>
     </row>
-    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="15.75" thickBot="1">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
         <f t="shared" si="0"/>
@@ -5472,7 +5519,7 @@
       </c>
       <c r="K101" s="9"/>
     </row>
-    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="15.75" thickBot="1">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
         <f>ROW(B102) - ROW($B$2)</f>
@@ -5504,7 +5551,7 @@
       </c>
       <c r="K102" s="7"/>
     </row>
-    <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="15.75" thickBot="1">
       <c r="A103" s="1"/>
       <c r="B103" s="11">
         <f t="shared" si="0"/>
@@ -5538,7 +5585,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="15.75" thickBot="1">
       <c r="A104" s="1"/>
       <c r="B104" s="11">
         <f>ROW(B104) - ROW($B$2)</f>
@@ -5570,7 +5617,7 @@
       </c>
       <c r="K104" s="7"/>
     </row>
-    <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="15.75" thickBot="1">
       <c r="A105" s="1"/>
       <c r="B105" s="11">
         <f t="shared" si="0"/>
@@ -5604,7 +5651,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="15.75" thickBot="1">
       <c r="A106" s="1"/>
       <c r="B106" s="11">
         <f>ROW(B106) - ROW($B$2)</f>
@@ -5636,7 +5683,7 @@
       </c>
       <c r="K106" s="7"/>
     </row>
-    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="15.75" thickBot="1">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
         <f t="shared" si="0"/>
@@ -5668,7 +5715,7 @@
       </c>
       <c r="K107" s="9"/>
     </row>
-    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="15.75" thickBot="1">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
         <f>ROW(B108) - ROW($B$2)</f>
@@ -5702,7 +5749,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="15.75" thickBot="1">
       <c r="A109" s="1"/>
       <c r="B109" s="11">
         <f t="shared" si="0"/>
@@ -5736,7 +5783,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="15.75" thickBot="1">
       <c r="A110" s="1"/>
       <c r="B110" s="11">
         <f t="shared" si="0"/>
@@ -5768,7 +5815,7 @@
       </c>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="24.75" thickBot="1">
       <c r="A111" s="1"/>
       <c r="B111" s="11">
         <f>ROW(B111) - ROW($B$2)</f>
@@ -5800,7 +5847,7 @@
       </c>
       <c r="K111" s="7"/>
     </row>
-    <row r="112" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="48.75" thickBot="1">
       <c r="A112" s="1"/>
       <c r="B112" s="11">
         <f t="shared" si="0"/>
@@ -5832,7 +5879,7 @@
       </c>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="36.75" thickBot="1">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
         <f>ROW(B113) - ROW($B$2)</f>
@@ -5864,7 +5911,7 @@
       </c>
       <c r="K113" s="7"/>
     </row>
-    <row r="114" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="24.75" thickBot="1">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
         <f t="shared" si="0"/>
@@ -5896,7 +5943,7 @@
       </c>
       <c r="K114" s="9"/>
     </row>
-    <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="15.75" thickBot="1">
       <c r="A115" s="1"/>
       <c r="B115" s="11">
         <f>ROW(B115) - ROW($B$2)</f>
@@ -5928,7 +5975,7 @@
       </c>
       <c r="K115" s="7"/>
     </row>
-    <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="15.75" thickBot="1">
       <c r="A116" s="1"/>
       <c r="B116" s="11">
         <f t="shared" si="0"/>
@@ -5960,7 +6007,7 @@
       </c>
       <c r="K116" s="9"/>
     </row>
-    <row r="117" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="24.75" thickBot="1">
       <c r="A117" s="1"/>
       <c r="B117" s="11">
         <f>ROW(B117) - ROW($B$2)</f>
@@ -5992,7 +6039,7 @@
       </c>
       <c r="K117" s="7"/>
     </row>
-    <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="15.75" thickBot="1">
       <c r="A118" s="1"/>
       <c r="B118" s="11">
         <f t="shared" si="0"/>
@@ -6024,7 +6071,7 @@
       </c>
       <c r="K118" s="9"/>
     </row>
-    <row r="119" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="15.75" thickBot="1">
       <c r="A119" s="1"/>
       <c r="B119" s="11">
         <f>ROW(B119) - ROW($B$2)</f>
@@ -6056,7 +6103,7 @@
       </c>
       <c r="K119" s="7"/>
     </row>
-    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="15.75" thickBot="1">
       <c r="A120" s="1"/>
       <c r="B120" s="11">
         <f t="shared" si="0"/>
@@ -6088,7 +6135,7 @@
       </c>
       <c r="K120" s="9"/>
     </row>
-    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="15.75" thickBot="1">
       <c r="A121" s="1"/>
       <c r="B121" s="11">
         <f>ROW(B121) - ROW($B$2)</f>
@@ -6120,7 +6167,7 @@
       </c>
       <c r="K121" s="7"/>
     </row>
-    <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="15.75" thickBot="1">
       <c r="A122" s="1"/>
       <c r="B122" s="11">
         <f t="shared" si="0"/>
@@ -6152,7 +6199,7 @@
       </c>
       <c r="K122" s="9"/>
     </row>
-    <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="15.75" thickBot="1">
       <c r="A123" s="1"/>
       <c r="B123" s="11">
         <f>ROW(B123) - ROW($B$2)</f>
@@ -6184,7 +6231,7 @@
       </c>
       <c r="K123" s="7"/>
     </row>
-    <row r="124" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="24.75" thickBot="1">
       <c r="A124" s="1"/>
       <c r="B124" s="11">
         <f t="shared" si="0"/>
@@ -6216,7 +6263,7 @@
       </c>
       <c r="K124" s="9"/>
     </row>
-    <row r="125" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="24.75" thickBot="1">
       <c r="A125" s="1"/>
       <c r="B125" s="11">
         <f>ROW(B125) - ROW($B$2)</f>
@@ -6248,7 +6295,7 @@
       </c>
       <c r="K125" s="7"/>
     </row>
-    <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="15.75" thickBot="1">
       <c r="A126" s="1"/>
       <c r="B126" s="11">
         <f t="shared" si="0"/>
@@ -6280,7 +6327,7 @@
       </c>
       <c r="K126" s="9"/>
     </row>
-    <row r="127" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="24.75" thickBot="1">
       <c r="A127" s="1"/>
       <c r="B127" s="11">
         <f>ROW(B127) - ROW($B$2)</f>
@@ -6312,7 +6359,7 @@
       </c>
       <c r="K127" s="7"/>
     </row>
-    <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="15.75" thickBot="1">
       <c r="A128" s="1"/>
       <c r="B128" s="11">
         <f t="shared" si="0"/>
@@ -6344,7 +6391,7 @@
       </c>
       <c r="K128" s="9"/>
     </row>
-    <row r="129" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="36.75" thickBot="1">
       <c r="A129" s="1"/>
       <c r="B129" s="11">
         <f t="shared" si="0"/>
@@ -6376,7 +6423,7 @@
       </c>
       <c r="K129" s="9"/>
     </row>
-    <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="15.75" thickBot="1">
       <c r="A130" s="1"/>
       <c r="B130" s="11">
         <f>ROW(B130) - ROW($B$2)</f>
@@ -6408,7 +6455,7 @@
       </c>
       <c r="K130" s="7"/>
     </row>
-    <row r="131" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="36.75" thickBot="1">
       <c r="A131" s="1"/>
       <c r="B131" s="11">
         <f t="shared" si="0"/>
@@ -6440,7 +6487,7 @@
       </c>
       <c r="K131" s="9"/>
     </row>
-    <row r="132" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="24.75" thickBot="1">
       <c r="B132" s="11">
         <f>ROW(B132) - ROW($B$2)</f>
         <v>130</v>
@@ -6471,7 +6518,7 @@
       </c>
       <c r="K132" s="7"/>
     </row>
-    <row r="133" spans="1:11" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="64.5" thickBot="1">
       <c r="B133" s="11">
         <f>ROW(B133) - ROW($B$2)</f>
         <v>131</v>
@@ -6504,9 +6551,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="36.75" thickBot="1">
       <c r="B134" s="11">
-        <f t="shared" ref="B134:B135" si="1">ROW(B134) - ROW($B$2)</f>
+        <f t="shared" ref="B134:B136" si="1">ROW(B134) - ROW($B$2)</f>
         <v>132</v>
       </c>
       <c r="C134" s="12" t="s">
@@ -6535,7 +6582,7 @@
       </c>
       <c r="K134" s="9"/>
     </row>
-    <row r="135" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="24.75" thickBot="1">
       <c r="B135" s="11">
         <f t="shared" si="1"/>
         <v>133</v>
@@ -6565,12 +6612,48 @@
         <v>2</v>
       </c>
       <c r="K135" s="9"/>
+    </row>
+    <row r="136" spans="1:11" ht="36.75" thickBot="1">
+      <c r="B136" s="11">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="I136" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="J136" s="9">
+        <v>1</v>
+      </c>
+      <c r="K136" s="19" t="s">
+        <v>564</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K136" r:id="rId1" location="nav-specification"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="566">
   <si>
     <t>#</t>
   </si>
@@ -306,9 +306,6 @@
     <t>R31</t>
   </si>
   <si>
-    <t>R39, R42, R45, R52, R55, R57, R58, R83, R84, R104</t>
-  </si>
-  <si>
     <t>R40</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>R46</t>
   </si>
   <si>
-    <t>R47, R48, R54, R60, R63, R85, R89, R100</t>
-  </si>
-  <si>
     <t>R49, R59, R62, R73</t>
   </si>
   <si>
@@ -375,9 +369,6 @@
     <t>R81, R86</t>
   </si>
   <si>
-    <t>R82, R110</t>
-  </si>
-  <si>
     <t>R87</t>
   </si>
   <si>
@@ -1714,6 +1705,18 @@
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>R39, R42, R45, R52, R55, R57, R58, R82, R84, R104</t>
+  </si>
+  <si>
+    <t>R47, R48, R54, R60, R63, R89, R100</t>
+  </si>
+  <si>
+    <t>R83, R110</t>
+  </si>
+  <si>
+    <t>R85</t>
   </si>
 </sst>
 </file>
@@ -1984,11 +1987,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2278,7 +2281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:U137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2291,9 +2294,13 @@
     <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2302,11 +2309,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2318,28 +2325,28 @@
         <v>26</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -2352,29 +2359,33 @@
         <v>27</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J3" s="7">
         <v>4</v>
       </c>
       <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U3" t="b">
+        <f>IF(P3=J3,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" thickBot="1">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B131" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B132" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -2384,26 +2395,30 @@
         <v>28</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J4" s="9">
         <v>10</v>
       </c>
       <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U4" t="b">
+        <f t="shared" ref="U4:U67" si="1">IF(P4=J4,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="24.75" thickBot="1">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -2413,29 +2428,33 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J5" s="7">
         <v>12</v>
       </c>
       <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:11" ht="48.75" thickBot="1">
+      <c r="U5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="48.75" thickBot="1">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -2445,29 +2464,33 @@
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J6" s="9">
         <v>30</v>
       </c>
       <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" thickBot="1">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -2480,26 +2503,30 @@
         <v>29</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
       </c>
       <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U7" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="24.75" thickBot="1">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -2512,26 +2539,30 @@
         <v>30</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J8" s="9">
         <v>12</v>
       </c>
       <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U8" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" thickBot="1">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -2544,26 +2575,30 @@
         <v>31</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
       </c>
       <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U9" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" thickBot="1">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -2576,26 +2611,30 @@
         <v>32</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
       </c>
       <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U10" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.75" thickBot="1">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -2608,26 +2647,30 @@
         <v>33</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
       </c>
       <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U11" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="24.75" thickBot="1">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -2640,26 +2683,30 @@
         <v>34</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J12" s="9">
         <v>9</v>
       </c>
       <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U12" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
@@ -2672,26 +2719,30 @@
         <v>35</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J13" s="7">
         <v>9</v>
       </c>
       <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U13" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15.75" thickBot="1">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -2704,26 +2755,30 @@
         <v>36</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J14" s="9">
         <v>2</v>
       </c>
       <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U14" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15.75" thickBot="1">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
@@ -2736,26 +2791,30 @@
         <v>37</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J15" s="7">
         <v>3</v>
       </c>
       <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U15" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15.75" thickBot="1">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -2768,26 +2827,30 @@
         <v>38</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
       </c>
       <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U16" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" thickBot="1">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
@@ -2800,26 +2863,30 @@
         <v>39</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
       </c>
       <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U17" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" thickBot="1">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <f t="shared" si="0"/>
@@ -2832,26 +2899,30 @@
         <v>40</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J18" s="9">
         <v>8</v>
       </c>
       <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U18" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15.75" thickBot="1">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -2864,26 +2935,30 @@
         <v>41</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="J19" s="7">
         <v>5</v>
       </c>
       <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U19" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" thickBot="1">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
         <f t="shared" si="0"/>
@@ -2896,26 +2971,30 @@
         <v>42</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
       </c>
       <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U20" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" thickBot="1">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
@@ -2928,26 +3007,30 @@
         <v>43</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J21" s="7">
         <v>3</v>
       </c>
       <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U21" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15.75" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
         <f t="shared" si="0"/>
@@ -2960,26 +3043,30 @@
         <v>44</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J22" s="9">
         <v>2</v>
       </c>
       <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U22" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15.75" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
@@ -2992,26 +3079,30 @@
         <v>45</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J23" s="7">
         <v>3</v>
       </c>
       <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U23" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="15.75" thickBot="1">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
@@ -3024,26 +3115,30 @@
         <v>46</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
       </c>
       <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U24" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="15.75" thickBot="1">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
         <f>ROW(B25) - ROW($B$2)</f>
@@ -3056,26 +3151,30 @@
         <v>47</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
       </c>
       <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U25" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="15.75" thickBot="1">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
@@ -3088,26 +3187,30 @@
         <v>48</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J26" s="9">
         <v>2</v>
       </c>
       <c r="K26" s="9"/>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U26" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" thickBot="1">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f>ROW(B27) - ROW($B$2)</f>
@@ -3120,26 +3223,30 @@
         <v>49</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
       </c>
       <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" thickBot="1">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
@@ -3152,26 +3259,30 @@
         <v>50</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
       </c>
       <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U28" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="15.75" thickBot="1">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
@@ -3184,26 +3295,30 @@
         <v>51</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J29" s="7">
         <v>8</v>
       </c>
       <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U29" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="15.75" thickBot="1">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
@@ -3216,26 +3331,30 @@
         <v>52</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J30" s="9">
         <v>1</v>
       </c>
       <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U30" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15.75" thickBot="1">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
@@ -3248,26 +3367,30 @@
         <v>53</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
       </c>
       <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U31" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="15.75" thickBot="1">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f t="shared" si="0"/>
@@ -3280,28 +3403,32 @@
         <v>54</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J32" s="14">
         <v>7</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U32" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" thickBot="1">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f>ROW(B33) - ROW($B$2)</f>
@@ -3314,28 +3441,32 @@
         <v>55</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="36.75" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U33" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="36.75" thickBot="1">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f t="shared" si="0"/>
@@ -3348,26 +3479,30 @@
         <v>56</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J34" s="9">
         <v>9</v>
       </c>
       <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U34" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="24.75" thickBot="1">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f>ROW(B35) - ROW($B$2)</f>
@@ -3380,26 +3515,30 @@
         <v>57</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J35" s="7">
         <v>1</v>
       </c>
       <c r="K35" s="7"/>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U35" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
@@ -3412,28 +3551,32 @@
         <v>58</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J36" s="14">
         <v>1</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U36" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="15.75" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f>ROW(B37) - ROW($B$2)</f>
@@ -3446,58 +3589,66 @@
         <v>59</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J37" s="7">
         <v>2</v>
       </c>
       <c r="K37" s="7"/>
-    </row>
-    <row r="38" spans="1:11" ht="36.75" thickBot="1">
+      <c r="U37" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="36.75" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>60</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G38" s="10">
         <v>5027740891</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J38" s="9">
         <v>1</v>
       </c>
       <c r="K38" s="9"/>
-    </row>
-    <row r="39" spans="1:11" ht="48.75" thickBot="1">
+      <c r="U38" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="48.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
@@ -3510,26 +3661,30 @@
         <v>61</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J39" s="7">
         <v>1</v>
       </c>
       <c r="K39" s="7"/>
-    </row>
-    <row r="40" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U39" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="24.75" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
@@ -3542,26 +3697,30 @@
         <v>62</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J40" s="9">
         <v>1</v>
       </c>
       <c r="K40" s="9"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U40" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" thickBot="1">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
@@ -3574,26 +3733,30 @@
         <v>63</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J41" s="7">
         <v>1</v>
       </c>
       <c r="K41" s="7"/>
-    </row>
-    <row r="42" spans="1:11" ht="26.25" thickBot="1">
+      <c r="U41" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="26.25" thickBot="1">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
@@ -3606,26 +3769,30 @@
         <v>64</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J42" s="9">
         <v>2</v>
       </c>
       <c r="K42" s="9"/>
-    </row>
-    <row r="43" spans="1:11" ht="26.25" thickBot="1">
+      <c r="U42" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="26.25" thickBot="1">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
@@ -3638,28 +3805,32 @@
         <v>65</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J43" s="14">
         <v>1</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="26.25" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U43" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="26.25" thickBot="1">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
@@ -3672,26 +3843,30 @@
         <v>66</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
       </c>
       <c r="K44" s="9"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U44" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="15.75" thickBot="1">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
@@ -3704,26 +3879,30 @@
         <v>67</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J45" s="9">
         <v>1</v>
       </c>
       <c r="K45" s="9"/>
-    </row>
-    <row r="46" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U45" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="24.75" thickBot="1">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f>ROW(B46) - ROW($B$2)</f>
@@ -3736,26 +3915,30 @@
         <v>68</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J46" s="7">
         <v>3</v>
       </c>
       <c r="K46" s="7"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U46" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f t="shared" si="0"/>
@@ -3768,26 +3951,30 @@
         <v>69</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J47" s="9">
         <v>1</v>
       </c>
       <c r="K47" s="9"/>
-    </row>
-    <row r="48" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U47" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="24.75" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f>ROW(B48) - ROW($B$2)</f>
@@ -3800,26 +3987,30 @@
         <v>70</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J48" s="7">
         <v>1</v>
       </c>
       <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U48" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="15.75" thickBot="1">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f t="shared" si="0"/>
@@ -3832,28 +4023,32 @@
         <v>71</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J49" s="14">
         <v>1</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="24.75" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U49" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="24.75" thickBot="1">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f>ROW(B50) - ROW($B$2)</f>
@@ -3866,26 +4061,30 @@
         <v>72</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J50" s="7">
         <v>1</v>
       </c>
       <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U50" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="24.75" thickBot="1">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f t="shared" si="0"/>
@@ -3895,29 +4094,33 @@
         <v>15</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J51" s="9">
         <v>5</v>
       </c>
       <c r="K51" s="9"/>
-    </row>
-    <row r="52" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U51" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="24.75" thickBot="1">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f>ROW(B52) - ROW($B$2)</f>
@@ -3930,26 +4133,30 @@
         <v>73</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J52" s="7">
         <v>2</v>
       </c>
       <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U52" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="15.75" thickBot="1">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f t="shared" si="0"/>
@@ -3962,26 +4169,30 @@
         <v>74</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J53" s="9">
         <v>1</v>
       </c>
       <c r="K53" s="9"/>
-    </row>
-    <row r="54" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U53" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="24.75" thickBot="1">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f>ROW(B54) - ROW($B$2)</f>
@@ -3994,26 +4205,30 @@
         <v>75</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J54" s="7">
         <v>1</v>
       </c>
       <c r="K54" s="7"/>
-    </row>
-    <row r="55" spans="1:11" ht="36.75" thickBot="1">
+      <c r="U54" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="36.75" thickBot="1">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f t="shared" si="0"/>
@@ -4026,26 +4241,30 @@
         <v>76</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J55" s="9">
         <v>1</v>
       </c>
       <c r="K55" s="9"/>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U55" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="15.75" thickBot="1">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f>ROW(B56) - ROW($B$2)</f>
@@ -4058,26 +4277,30 @@
         <v>77</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J56" s="7">
         <v>1</v>
       </c>
       <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U56" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="15.75" thickBot="1">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f t="shared" si="0"/>
@@ -4090,26 +4313,30 @@
         <v>78</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J57" s="9">
         <v>6</v>
       </c>
       <c r="K57" s="9"/>
-    </row>
-    <row r="58" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U57" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="15.75" thickBot="1">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f>ROW(B58) - ROW($B$2)</f>
@@ -4122,26 +4349,30 @@
         <v>79</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J58" s="7">
         <v>7</v>
       </c>
       <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U58" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="15.75" thickBot="1">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f t="shared" si="0"/>
@@ -4154,26 +4385,30 @@
         <v>80</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J59" s="9">
         <v>1</v>
       </c>
       <c r="K59" s="9"/>
-    </row>
-    <row r="60" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U59" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="15.75" thickBot="1">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f>ROW(B60) - ROW($B$2)</f>
@@ -4186,26 +4421,30 @@
         <v>81</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J60" s="7">
         <v>1</v>
       </c>
       <c r="K60" s="7"/>
-    </row>
-    <row r="61" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U60" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="15.75" thickBot="1">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f t="shared" si="0"/>
@@ -4218,26 +4457,30 @@
         <v>82</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J61" s="9">
         <v>1</v>
       </c>
       <c r="K61" s="9"/>
-    </row>
-    <row r="62" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U61" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="15.75" thickBot="1">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f>ROW(B62) - ROW($B$2)</f>
@@ -4250,26 +4493,30 @@
         <v>83</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J62" s="7">
         <v>1</v>
       </c>
       <c r="K62" s="7"/>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U62" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="15.75" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f t="shared" si="0"/>
@@ -4282,26 +4529,30 @@
         <v>84</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J63" s="9">
         <v>1</v>
       </c>
       <c r="K63" s="9"/>
-    </row>
-    <row r="64" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U63" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="15.75" thickBot="1">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f>ROW(B64) - ROW($B$2)</f>
@@ -4314,26 +4565,30 @@
         <v>85</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J64" s="7">
         <v>1</v>
       </c>
       <c r="K64" s="7"/>
-    </row>
-    <row r="65" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U64" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="15.75" thickBot="1">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f t="shared" si="0"/>
@@ -4346,26 +4601,30 @@
         <v>86</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J65" s="9">
         <v>1</v>
       </c>
       <c r="K65" s="9"/>
-    </row>
-    <row r="66" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U65" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="15.75" thickBot="1">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f>ROW(B66) - ROW($B$2)</f>
@@ -4378,26 +4637,30 @@
         <v>87</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J66" s="7">
         <v>1</v>
       </c>
       <c r="K66" s="7"/>
-    </row>
-    <row r="67" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U66" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="15.75" thickBot="1">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="0"/>
@@ -4410,26 +4673,30 @@
         <v>88</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J67" s="9">
         <v>1</v>
       </c>
       <c r="K67" s="9"/>
-    </row>
-    <row r="68" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U67" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="15.75" thickBot="1">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f>ROW(B68) - ROW($B$2)</f>
@@ -4442,26 +4709,30 @@
         <v>89</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J68" s="7">
         <v>1</v>
       </c>
       <c r="K68" s="7"/>
-    </row>
-    <row r="69" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U68" t="b">
+        <f t="shared" ref="U68:U131" si="2">IF(P68=J68,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="15.75" thickBot="1">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="0"/>
@@ -4471,29 +4742,33 @@
         <v>18</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J69" s="9">
         <v>6</v>
       </c>
       <c r="K69" s="9"/>
-    </row>
-    <row r="70" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U69" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="15.75" thickBot="1">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f>ROW(B70) - ROW($B$2)</f>
@@ -4506,26 +4781,30 @@
         <v>90</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J70" s="7">
         <v>1</v>
       </c>
       <c r="K70" s="7"/>
-    </row>
-    <row r="71" spans="1:11" ht="36.75" thickBot="1">
+      <c r="U70" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="36.75" thickBot="1">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f t="shared" si="0"/>
@@ -4538,26 +4817,30 @@
         <v>91</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J71" s="9">
         <v>19</v>
       </c>
       <c r="K71" s="9"/>
-    </row>
-    <row r="72" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U71" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15.75" thickBot="1">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f>ROW(B72) - ROW($B$2)</f>
@@ -4570,26 +4853,30 @@
         <v>92</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J72" s="7">
         <v>2</v>
       </c>
       <c r="K72" s="7"/>
-    </row>
-    <row r="73" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U72" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="15.75" thickBot="1">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f t="shared" si="0"/>
@@ -4602,26 +4889,30 @@
         <v>93</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J73" s="9">
         <v>1</v>
       </c>
       <c r="K73" s="9"/>
-    </row>
-    <row r="74" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U73" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="15.75" thickBot="1">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f>ROW(B74) - ROW($B$2)</f>
@@ -4634,26 +4925,30 @@
         <v>94</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J74" s="7">
         <v>1</v>
       </c>
       <c r="K74" s="7"/>
-    </row>
-    <row r="75" spans="1:11" ht="24.75" thickBot="1">
+      <c r="U74" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="24.75" thickBot="1">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f t="shared" si="0"/>
@@ -4663,29 +4958,33 @@
         <v>18</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>95</v>
+        <v>562</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J75" s="9">
         <v>10</v>
       </c>
       <c r="K75" s="9"/>
-    </row>
-    <row r="76" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U75" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="15.75" thickBot="1">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f>ROW(B76) - ROW($B$2)</f>
@@ -4695,29 +4994,33 @@
         <v>19</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J76" s="7">
         <v>1</v>
       </c>
       <c r="K76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U76" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="15.75" thickBot="1">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f t="shared" si="0"/>
@@ -4727,29 +5030,33 @@
         <v>18</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J77" s="9">
         <v>1</v>
       </c>
       <c r="K77" s="9"/>
-    </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U77" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="15.75" thickBot="1">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f>ROW(B78) - ROW($B$2)</f>
@@ -4759,29 +5066,33 @@
         <v>19</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J78" s="7">
         <v>1</v>
       </c>
       <c r="K78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U78" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="15.75" thickBot="1">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f t="shared" si="0"/>
@@ -4791,29 +5102,33 @@
         <v>19</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J79" s="9">
         <v>1</v>
       </c>
       <c r="K79" s="9"/>
-    </row>
-    <row r="80" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U79" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="15.75" thickBot="1">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f>ROW(B80) - ROW($B$2)</f>
@@ -4823,29 +5138,33 @@
         <v>19</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J80" s="7">
         <v>1</v>
       </c>
       <c r="K80" s="7"/>
-    </row>
-    <row r="81" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U80" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="15.75" thickBot="1">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="0"/>
@@ -4855,29 +5174,33 @@
         <v>18</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>101</v>
+        <v>563</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J81" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K81" s="9"/>
-    </row>
-    <row r="82" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U81" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="15.75" thickBot="1">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f>ROW(B82) - ROW($B$2)</f>
@@ -4887,29 +5210,33 @@
         <v>18</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J82" s="7">
         <v>4</v>
       </c>
       <c r="K82" s="7"/>
-    </row>
-    <row r="83" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U82" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="15.75" thickBot="1">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f t="shared" si="0"/>
@@ -4919,29 +5246,33 @@
         <v>19</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J83" s="9">
         <v>5</v>
       </c>
       <c r="K83" s="9"/>
-    </row>
-    <row r="84" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U83" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="15.75" thickBot="1">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f>ROW(B84) - ROW($B$2)</f>
@@ -4951,29 +5282,33 @@
         <v>19</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J84" s="7">
         <v>1</v>
       </c>
       <c r="K84" s="7"/>
-    </row>
-    <row r="85" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U84" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="15.75" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f t="shared" si="0"/>
@@ -4983,29 +5318,33 @@
         <v>19</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J85" s="9">
         <v>2</v>
       </c>
       <c r="K85" s="9"/>
-    </row>
-    <row r="86" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U85" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="15.75" thickBot="1">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f>ROW(B86) - ROW($B$2)</f>
@@ -5015,29 +5354,33 @@
         <v>18</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J86" s="7">
         <v>1</v>
       </c>
       <c r="K86" s="7"/>
-    </row>
-    <row r="87" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U86" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="15.75" thickBot="1">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
         <f t="shared" si="0"/>
@@ -5047,29 +5390,33 @@
         <v>18</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J87" s="9">
         <v>1</v>
       </c>
       <c r="K87" s="9"/>
-    </row>
-    <row r="88" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U87" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="15.75" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f>ROW(B88) - ROW($B$2)</f>
@@ -5079,29 +5426,33 @@
         <v>19</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J88" s="7">
         <v>1</v>
       </c>
       <c r="K88" s="7"/>
-    </row>
-    <row r="89" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U88" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="15.75" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
         <f t="shared" si="0"/>
@@ -5111,29 +5462,33 @@
         <v>19</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J89" s="9">
         <v>1</v>
       </c>
       <c r="K89" s="9"/>
-    </row>
-    <row r="90" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U89" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="15.75" thickBot="1">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f>ROW(B90) - ROW($B$2)</f>
@@ -5143,29 +5498,33 @@
         <v>19</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J90" s="7">
         <v>1</v>
       </c>
       <c r="K90" s="7"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U90" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="15.75" thickBot="1">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f t="shared" si="0"/>
@@ -5175,29 +5534,33 @@
         <v>18</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J91" s="9">
         <v>1</v>
       </c>
       <c r="K91" s="9"/>
-    </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U91" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" ht="15.75" thickBot="1">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f>ROW(B92) - ROW($B$2)</f>
@@ -5207,29 +5570,33 @@
         <v>19</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J92" s="7">
         <v>3</v>
       </c>
       <c r="K92" s="7"/>
-    </row>
-    <row r="93" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U92" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="15.75" thickBot="1">
       <c r="A93" s="1"/>
       <c r="B93" s="11">
         <f t="shared" si="0"/>
@@ -5239,29 +5606,33 @@
         <v>18</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J93" s="9">
         <v>6</v>
       </c>
       <c r="K93" s="9"/>
-    </row>
-    <row r="94" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U93" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="15.75" thickBot="1">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
         <f>ROW(B94) - ROW($B$2)</f>
@@ -5271,29 +5642,33 @@
         <v>18</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J94" s="7">
         <v>1</v>
       </c>
       <c r="K94" s="7"/>
-    </row>
-    <row r="95" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U94" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" ht="15.75" thickBot="1">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
         <f t="shared" si="0"/>
@@ -5303,29 +5678,33 @@
         <v>18</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J95" s="9">
         <v>1</v>
       </c>
       <c r="K95" s="9"/>
-    </row>
-    <row r="96" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U95" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="15.75" thickBot="1">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f>ROW(B96) - ROW($B$2)</f>
@@ -5335,29 +5714,33 @@
         <v>18</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J96" s="7">
         <v>1</v>
       </c>
       <c r="K96" s="7"/>
-    </row>
-    <row r="97" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U96" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="15.75" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="11">
         <f t="shared" si="0"/>
@@ -5367,29 +5750,33 @@
         <v>18</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J97" s="9">
         <v>2</v>
       </c>
       <c r="K97" s="9"/>
-    </row>
-    <row r="98" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U97" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="15.75" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
         <f>ROW(B98) - ROW($B$2)</f>
@@ -5399,391 +5786,439 @@
         <v>18</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>118</v>
+        <v>564</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H98" s="14" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I98" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J98" s="14">
         <v>2</v>
       </c>
       <c r="K98" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="36.75" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U98" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" ht="15.75" thickBot="1">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B99) - ROW($B$2)</f>
         <v>97</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="I99" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="J99" s="9">
-        <v>1</v>
-      </c>
-      <c r="K99" s="9"/>
-    </row>
-    <row r="100" spans="1:11" ht="15.75" thickBot="1">
+        <v>18</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J99" s="14">
+        <v>1</v>
+      </c>
+      <c r="K99" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="U99" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="36.75" thickBot="1">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
-        <f>ROW(B100) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="J100" s="7">
-        <v>1</v>
-      </c>
-      <c r="K100" s="7"/>
-    </row>
-    <row r="101" spans="1:11" ht="15.75" thickBot="1">
+      <c r="D100" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J100" s="9">
+        <v>1</v>
+      </c>
+      <c r="K100" s="9"/>
+      <c r="U100" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="15.75" thickBot="1">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B101) - ROW($B$2)</f>
         <v>99</v>
       </c>
-      <c r="C101" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="I101" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="J101" s="9">
-        <v>1</v>
-      </c>
-      <c r="K101" s="9"/>
-    </row>
-    <row r="102" spans="1:11" ht="15.75" thickBot="1">
+      <c r="C101" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J101" s="7">
+        <v>1</v>
+      </c>
+      <c r="K101" s="7"/>
+      <c r="U101" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="15.75" thickBot="1">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
-        <f>ROW(B102) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I102" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="J102" s="7">
-        <v>1</v>
-      </c>
-      <c r="K102" s="7"/>
-    </row>
-    <row r="103" spans="1:11" ht="15.75" thickBot="1">
+      <c r="D102" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="J102" s="9">
+        <v>1</v>
+      </c>
+      <c r="K102" s="9"/>
+      <c r="U102" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" ht="15.75" thickBot="1">
       <c r="A103" s="1"/>
       <c r="B103" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B103) - ROW($B$2)</f>
         <v>101</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D103" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="H103" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="I103" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="J103" s="14">
-        <v>1</v>
-      </c>
-      <c r="K103" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="15.75" thickBot="1">
+      <c r="D103" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="J103" s="7">
+        <v>1</v>
+      </c>
+      <c r="K103" s="7"/>
+      <c r="U103" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="15.75" thickBot="1">
       <c r="A104" s="1"/>
       <c r="B104" s="11">
-        <f>ROW(B104) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="C104" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="J104" s="7">
-        <v>1</v>
-      </c>
-      <c r="K104" s="7"/>
-    </row>
-    <row r="105" spans="1:11" ht="15.75" thickBot="1">
+      <c r="C104" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J104" s="14">
+        <v>1</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="U104" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="15.75" thickBot="1">
       <c r="A105" s="1"/>
       <c r="B105" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B105) - ROW($B$2)</f>
         <v>103</v>
       </c>
-      <c r="C105" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E105" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="G105" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="I105" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="J105" s="14">
-        <v>1</v>
-      </c>
-      <c r="K105" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="15.75" thickBot="1">
+      <c r="C105" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="J105" s="7">
+        <v>1</v>
+      </c>
+      <c r="K105" s="7"/>
+      <c r="U105" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="15.75" thickBot="1">
       <c r="A106" s="1"/>
       <c r="B106" s="11">
-        <f>ROW(B106) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="J106" s="7">
-        <v>4</v>
-      </c>
-      <c r="K106" s="7"/>
-    </row>
-    <row r="107" spans="1:11" ht="15.75" thickBot="1">
+      <c r="D106" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G106" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J106" s="14">
+        <v>1</v>
+      </c>
+      <c r="K106" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="U106" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="15.75" thickBot="1">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B107) - ROW($B$2)</f>
         <v>105</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D107" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="I107" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="J107" s="9">
-        <v>1</v>
-      </c>
-      <c r="K107" s="9"/>
-    </row>
-    <row r="108" spans="1:11" ht="15.75" thickBot="1">
+      <c r="D107" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="J107" s="7">
+        <v>4</v>
+      </c>
+      <c r="K107" s="7"/>
+      <c r="U107" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="15.75" thickBot="1">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
-        <f>ROW(B108) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D108" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E108" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="F108" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="G108" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="H108" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="I108" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="J108" s="14">
-        <v>1</v>
-      </c>
-      <c r="K108" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="15.75" thickBot="1">
+      <c r="D108" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I108" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="J108" s="9">
+        <v>1</v>
+      </c>
+      <c r="K108" s="9"/>
+      <c r="U108" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" ht="15.75" thickBot="1">
       <c r="A109" s="1"/>
       <c r="B109" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B109) - ROW($B$2)</f>
         <v>107</v>
       </c>
-      <c r="C109" s="13" t="s">
-        <v>19</v>
+      <c r="C109" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G109" s="15" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="H109" s="14" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I109" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J109" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K109" s="16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="15.75" thickBot="1">
+        <v>536</v>
+      </c>
+      <c r="U109" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" ht="15.75" thickBot="1">
       <c r="A110" s="1"/>
       <c r="B110" s="11">
         <f t="shared" si="0"/>
@@ -5792,858 +6227,1003 @@
       <c r="C110" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D110" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="I110" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="J110" s="9">
-        <v>1</v>
-      </c>
-      <c r="K110" s="9"/>
-    </row>
-    <row r="111" spans="1:11" ht="24.75" thickBot="1">
+      <c r="D110" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F110" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G110" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="H110" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J110" s="14">
+        <v>2</v>
+      </c>
+      <c r="K110" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="U110" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" ht="15.75" thickBot="1">
       <c r="A111" s="1"/>
       <c r="B111" s="11">
-        <f>ROW(B111) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="C111" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J111" s="7">
-        <v>1</v>
-      </c>
-      <c r="K111" s="7"/>
-    </row>
-    <row r="112" spans="1:11" ht="48.75" thickBot="1">
+      <c r="C111" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="J111" s="9">
+        <v>1</v>
+      </c>
+      <c r="K111" s="9"/>
+      <c r="U111" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="24.75" thickBot="1">
       <c r="A112" s="1"/>
       <c r="B112" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B112) - ROW($B$2)</f>
         <v>110</v>
       </c>
-      <c r="C112" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>255</v>
+      <c r="C112" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="G112" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="H112" s="9" t="s">
-        <v>454</v>
+        <v>537</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>450</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J112" s="9">
-        <v>1</v>
-      </c>
-      <c r="K112" s="9"/>
-    </row>
-    <row r="113" spans="1:11" ht="36.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J112" s="7">
+        <v>1</v>
+      </c>
+      <c r="K112" s="7"/>
+      <c r="U112" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" ht="48.75" thickBot="1">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
-        <f>ROW(B113) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>256</v>
+      <c r="D113" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>454</v>
+        <v>537</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>451</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J113" s="7">
-        <v>4</v>
-      </c>
-      <c r="K113" s="7"/>
-    </row>
-    <row r="114" spans="1:11" ht="24.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J113" s="9">
+        <v>1</v>
+      </c>
+      <c r="K113" s="9"/>
+      <c r="U113" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" ht="36.75" thickBot="1">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B114) - ROW($B$2)</f>
         <v>112</v>
       </c>
-      <c r="C114" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="G114" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="H114" s="9" t="s">
-        <v>455</v>
+      <c r="C114" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>451</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J114" s="9">
-        <v>1</v>
-      </c>
-      <c r="K114" s="9"/>
-    </row>
-    <row r="115" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J114" s="7">
+        <v>4</v>
+      </c>
+      <c r="K114" s="7"/>
+      <c r="U114" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" ht="24.75" thickBot="1">
       <c r="A115" s="1"/>
       <c r="B115" s="11">
-        <f>ROW(B115) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="C115" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D115" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="G115" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>456</v>
+      <c r="D115" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>452</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J115" s="7">
-        <v>1</v>
-      </c>
-      <c r="K115" s="7"/>
-    </row>
-    <row r="116" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J115" s="9">
+        <v>1</v>
+      </c>
+      <c r="K115" s="9"/>
+      <c r="U115" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" ht="15.75" thickBot="1">
       <c r="A116" s="1"/>
       <c r="B116" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B116) - ROW($B$2)</f>
         <v>114</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="H116" s="9" t="s">
-        <v>457</v>
+      <c r="D116" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J116" s="9">
-        <v>1</v>
-      </c>
-      <c r="K116" s="9"/>
-    </row>
-    <row r="117" spans="1:11" ht="24.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J116" s="7">
+        <v>1</v>
+      </c>
+      <c r="K116" s="7"/>
+      <c r="U116" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" ht="15.75" thickBot="1">
       <c r="A117" s="1"/>
       <c r="B117" s="11">
-        <f>ROW(B117) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G117" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>458</v>
+      <c r="D117" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>454</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J117" s="7">
-        <v>1</v>
-      </c>
-      <c r="K117" s="7"/>
-    </row>
-    <row r="118" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J117" s="9">
+        <v>1</v>
+      </c>
+      <c r="K117" s="9"/>
+      <c r="U117" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" ht="24.75" thickBot="1">
       <c r="A118" s="1"/>
       <c r="B118" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B118) - ROW($B$2)</f>
         <v>116</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C118" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D118" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="H118" s="9" t="s">
-        <v>459</v>
+      <c r="D118" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J118" s="9">
-        <v>1</v>
-      </c>
-      <c r="K118" s="9"/>
-    </row>
-    <row r="119" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J118" s="7">
+        <v>1</v>
+      </c>
+      <c r="K118" s="7"/>
+      <c r="U118" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" ht="15.75" thickBot="1">
       <c r="A119" s="1"/>
       <c r="B119" s="11">
-        <f>ROW(B119) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D119" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>459</v>
+      <c r="D119" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>456</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J119" s="7">
-        <v>1</v>
-      </c>
-      <c r="K119" s="7"/>
-    </row>
-    <row r="120" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J119" s="9">
+        <v>1</v>
+      </c>
+      <c r="K119" s="9"/>
+      <c r="U119" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" ht="15.75" thickBot="1">
       <c r="A120" s="1"/>
       <c r="B120" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B120) - ROW($B$2)</f>
         <v>118</v>
       </c>
-      <c r="C120" s="13" t="s">
+      <c r="C120" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D120" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>459</v>
+      <c r="D120" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J120" s="9">
-        <v>1</v>
-      </c>
-      <c r="K120" s="9"/>
-    </row>
-    <row r="121" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J120" s="7">
+        <v>1</v>
+      </c>
+      <c r="K120" s="7"/>
+      <c r="U120" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" ht="15.75" thickBot="1">
       <c r="A121" s="1"/>
       <c r="B121" s="11">
-        <f>ROW(B121) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>119</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D121" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>459</v>
+      <c r="D121" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>456</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J121" s="7">
-        <v>1</v>
-      </c>
-      <c r="K121" s="7"/>
-    </row>
-    <row r="122" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J121" s="9">
+        <v>1</v>
+      </c>
+      <c r="K121" s="9"/>
+      <c r="U121" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" ht="15.75" thickBot="1">
       <c r="A122" s="1"/>
       <c r="B122" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B122) - ROW($B$2)</f>
         <v>120</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D122" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F122" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>460</v>
+      <c r="D122" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J122" s="9">
-        <v>1</v>
-      </c>
-      <c r="K122" s="9"/>
-    </row>
-    <row r="123" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J122" s="7">
+        <v>1</v>
+      </c>
+      <c r="K122" s="7"/>
+      <c r="U122" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" ht="15.75" thickBot="1">
       <c r="A123" s="1"/>
       <c r="B123" s="11">
-        <f>ROW(B123) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="G123" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>459</v>
+      <c r="D123" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>457</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J123" s="7">
-        <v>1</v>
-      </c>
-      <c r="K123" s="7"/>
-    </row>
-    <row r="124" spans="1:11" ht="24.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J123" s="9">
+        <v>1</v>
+      </c>
+      <c r="K123" s="9"/>
+      <c r="U123" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" ht="15.75" thickBot="1">
       <c r="A124" s="1"/>
       <c r="B124" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B124) - ROW($B$2)</f>
         <v>122</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D124" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="G124" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>461</v>
+      <c r="D124" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J124" s="9">
-        <v>1</v>
-      </c>
-      <c r="K124" s="9"/>
-    </row>
-    <row r="125" spans="1:11" ht="24.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J124" s="7">
+        <v>1</v>
+      </c>
+      <c r="K124" s="7"/>
+      <c r="U124" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" ht="24.75" thickBot="1">
       <c r="A125" s="1"/>
       <c r="B125" s="11">
-        <f>ROW(B125) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="C125" s="12" t="s">
+      <c r="C125" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D125" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G125" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>459</v>
+      <c r="D125" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>458</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J125" s="7">
-        <v>1</v>
-      </c>
-      <c r="K125" s="7"/>
-    </row>
-    <row r="126" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J125" s="9">
+        <v>1</v>
+      </c>
+      <c r="K125" s="9"/>
+      <c r="U125" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" ht="24.75" thickBot="1">
       <c r="A126" s="1"/>
       <c r="B126" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B126) - ROW($B$2)</f>
         <v>124</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="H126" s="9" t="s">
-        <v>459</v>
+      <c r="D126" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J126" s="9">
-        <v>1</v>
-      </c>
-      <c r="K126" s="9"/>
-    </row>
-    <row r="127" spans="1:11" ht="24.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J126" s="7">
+        <v>1</v>
+      </c>
+      <c r="K126" s="7"/>
+      <c r="U126" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" ht="15.75" thickBot="1">
       <c r="A127" s="1"/>
       <c r="B127" s="11">
-        <f>ROW(B127) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D127" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>462</v>
+      <c r="D127" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>456</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J127" s="7">
-        <v>1</v>
-      </c>
-      <c r="K127" s="7"/>
-    </row>
-    <row r="128" spans="1:11" ht="15.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J127" s="9">
+        <v>1</v>
+      </c>
+      <c r="K127" s="9"/>
+      <c r="U127" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" ht="24.75" thickBot="1">
       <c r="A128" s="1"/>
       <c r="B128" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B128) - ROW($B$2)</f>
         <v>126</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="C128" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D128" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="G128" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="H128" s="9" t="s">
+      <c r="D128" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="H128" s="7" t="s">
         <v>459</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J128" s="9">
-        <v>1</v>
-      </c>
-      <c r="K128" s="9"/>
-    </row>
-    <row r="129" spans="1:11" ht="36.75" thickBot="1">
+        <v>538</v>
+      </c>
+      <c r="J128" s="7">
+        <v>1</v>
+      </c>
+      <c r="K128" s="7"/>
+      <c r="U128" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" ht="15.75" thickBot="1">
       <c r="A129" s="1"/>
       <c r="B129" s="11">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="I129" s="10" t="s">
-        <v>533</v>
+        <v>456</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>538</v>
       </c>
       <c r="J129" s="9">
         <v>1</v>
       </c>
       <c r="K129" s="9"/>
-    </row>
-    <row r="130" spans="1:11" ht="15.75" thickBot="1">
+      <c r="U129" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" ht="36.75" thickBot="1">
       <c r="A130" s="1"/>
       <c r="B130" s="11">
-        <f>ROW(B130) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="I130" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="J130" s="7">
-        <v>2</v>
-      </c>
-      <c r="K130" s="7"/>
-    </row>
-    <row r="131" spans="1:11" ht="36.75" thickBot="1">
+      <c r="C130" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="J130" s="9">
+        <v>1</v>
+      </c>
+      <c r="K130" s="9"/>
+      <c r="U130" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" ht="15.75" thickBot="1">
       <c r="A131" s="1"/>
       <c r="B131" s="11">
+        <f>ROW(B131) - ROW($B$2)</f>
+        <v>129</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="J131" s="7">
+        <v>2</v>
+      </c>
+      <c r="K131" s="7"/>
+      <c r="U131" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" ht="36.75" thickBot="1">
+      <c r="B132" s="11">
         <f t="shared" si="0"/>
-        <v>129</v>
-      </c>
-      <c r="C131" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C132" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="F131" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G131" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="I131" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="J131" s="9">
-        <v>1</v>
-      </c>
-      <c r="K131" s="9"/>
-    </row>
-    <row r="132" spans="1:11" ht="24.75" thickBot="1">
-      <c r="B132" s="11">
-        <f>ROW(B132) - ROW($B$2)</f>
-        <v>130</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J132" s="7">
-        <v>2</v>
-      </c>
-      <c r="K132" s="7"/>
-    </row>
-    <row r="133" spans="1:11" ht="64.5" thickBot="1">
+      <c r="D132" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="J132" s="9">
+        <v>1</v>
+      </c>
+      <c r="K132" s="9"/>
+      <c r="U132" t="b">
+        <f t="shared" ref="T132:U137" si="3">IF(P132=J132,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" ht="24.75" thickBot="1">
       <c r="B133" s="11">
         <f>ROW(B133) - ROW($B$2)</f>
         <v>131</v>
       </c>
       <c r="C133" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="H133" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="D133" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="E133" s="8" t="s">
+      <c r="I133" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="J133" s="7">
+        <v>2</v>
+      </c>
+      <c r="K133" s="7"/>
+      <c r="U133" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" ht="64.5" thickBot="1">
+      <c r="B134" s="11">
+        <f>ROW(B134) - ROW($B$2)</f>
+        <v>132</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="J134" s="7">
+        <v>1</v>
+      </c>
+      <c r="K134" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="U134" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" ht="36.75" thickBot="1">
+      <c r="B135" s="11">
+        <f t="shared" ref="B135:B137" si="4">ROW(B135) - ROW($B$2)</f>
+        <v>133</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="G135" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="F133" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="H133" s="7" t="s">
+      <c r="H135" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="I133" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="J133" s="7">
-        <v>1</v>
-      </c>
-      <c r="K133" s="17" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="36.75" thickBot="1">
-      <c r="B134" s="11">
-        <f t="shared" ref="B134:B136" si="1">ROW(B134) - ROW($B$2)</f>
-        <v>132</v>
-      </c>
-      <c r="C134" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="F134" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="I134" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="J134" s="9">
-        <v>1</v>
-      </c>
-      <c r="K134" s="9"/>
-    </row>
-    <row r="135" spans="1:11" ht="24.75" thickBot="1">
-      <c r="B135" s="11">
-        <f t="shared" si="1"/>
-        <v>133</v>
-      </c>
-      <c r="C135" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="E135" s="10" t="s">
+      <c r="I135" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J135" s="9">
+        <v>1</v>
+      </c>
+      <c r="K135" s="9"/>
+      <c r="U135" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" ht="24.75" thickBot="1">
+      <c r="B136" s="11">
+        <f t="shared" si="4"/>
+        <v>134</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="I136" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J136" s="9">
+        <v>2</v>
+      </c>
+      <c r="K136" s="9"/>
+      <c r="U136" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" ht="36.75" thickBot="1">
+      <c r="B137" s="11">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E137" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="F135" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="G135" s="10" t="s">
+      <c r="F137" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="G137" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="H135" s="9" t="s">
+      <c r="H137" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="I135" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="J135" s="9">
-        <v>2</v>
-      </c>
-      <c r="K135" s="9"/>
-    </row>
-    <row r="136" spans="1:11" ht="36.75" thickBot="1">
-      <c r="B136" s="11">
-        <f t="shared" si="1"/>
-        <v>134</v>
-      </c>
-      <c r="C136" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="E136" s="10" t="s">
+      <c r="I137" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J137" s="9">
+        <v>1</v>
+      </c>
+      <c r="K137" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="F136" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="I136" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="J136" s="9">
-        <v>1</v>
-      </c>
-      <c r="K136" s="19" t="s">
-        <v>564</v>
+      <c r="U137" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6651,7 +7231,7 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K136" r:id="rId1" location="nav-specification"/>
+    <hyperlink ref="K137" r:id="rId1" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="570">
   <si>
     <t>#</t>
   </si>
@@ -1717,6 +1717,18 @@
   </si>
   <si>
     <t>R85</t>
+  </si>
+  <si>
+    <t>5 inch TFT LCD Display 800*480 RGB Interface LCD Touch Screen Panel</t>
+  </si>
+  <si>
+    <t>RGB5001</t>
+  </si>
+  <si>
+    <t>QDTFT</t>
+  </si>
+  <si>
+    <t>Alibaba</t>
   </si>
 </sst>
 </file>
@@ -2281,7 +2293,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U137"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -7043,7 +7055,7 @@
       </c>
       <c r="K132" s="9"/>
       <c r="U132" t="b">
-        <f t="shared" ref="T132:U137" si="3">IF(P132=J132,TRUE,FALSE)</f>
+        <f t="shared" ref="U132:U138" si="3">IF(P132=J132,TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7121,7 +7133,7 @@
     </row>
     <row r="135" spans="1:21" ht="36.75" thickBot="1">
       <c r="B135" s="11">
-        <f t="shared" ref="B135:B137" si="4">ROW(B135) - ROW($B$2)</f>
+        <f t="shared" ref="B135:B138" si="4">ROW(B135) - ROW($B$2)</f>
         <v>133</v>
       </c>
       <c r="C135" s="12" t="s">
@@ -7222,6 +7234,43 @@
         <v>561</v>
       </c>
       <c r="U137" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" ht="24.75" thickBot="1">
+      <c r="B138" s="11">
+        <f t="shared" si="4"/>
+        <v>136</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="I138" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J138" s="9">
+        <v>1</v>
+      </c>
+      <c r="K138" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="U138" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7232,8 +7281,9 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K137" r:id="rId1" location="nav-specification"/>
+    <hyperlink ref="K138" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/Client-BOM-OFP_MCM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="573">
   <si>
     <t>#</t>
   </si>
@@ -1671,9 +1671,6 @@
     <t>0.3mm 40P 0.5mm Same Side 10cm P=0.5mm FFC Cable (Flexible Flat Cable) ROHS</t>
   </si>
   <si>
-    <t>C4, C11, C16, C20, C33, C37, C41, C57, C58, C93, C94, C149</t>
-  </si>
-  <si>
     <t>C7, C12, C13, C14, C15, C18, C19, C24, C27, C28, C29, C30, C31, C35, C36, C39, C40, C43, C44, C46, C95, C97, C111, C114, C117, C120, C124, C127, C130, C133</t>
   </si>
   <si>
@@ -1729,6 +1726,18 @@
   </si>
   <si>
     <t>Alibaba</t>
+  </si>
+  <si>
+    <t>C4, C11, C16, C20, C33, C37, C41, C57, C58, C93, C94</t>
+  </si>
+  <si>
+    <t>C149</t>
+  </si>
+  <si>
+    <t>GRM188R61E106KA73D</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 25V X5R 0603</t>
   </si>
 </sst>
 </file>
@@ -2293,7 +2302,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:U139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2397,7 +2406,7 @@
     <row r="4" spans="1:21" ht="15.75" thickBot="1">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B132" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B133" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -2426,7 +2435,7 @@
       </c>
       <c r="K4" s="9"/>
       <c r="U4" t="b">
-        <f t="shared" ref="U4:U67" si="1">IF(P4=J4,TRUE,FALSE)</f>
+        <f t="shared" ref="U4:U68" si="1">IF(P4=J4,TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2440,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>152</v>
@@ -2458,7 +2467,7 @@
         <v>465</v>
       </c>
       <c r="J5" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="7"/>
       <c r="U5" t="b">
@@ -2476,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>153</v>
@@ -3478,111 +3487,109 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="36.75" thickBot="1">
+    <row r="34" spans="1:21" ht="15.75" thickBot="1">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B34) - ROW($B$2)</f>
         <v>32</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>5</v>
+      <c r="C34" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>180</v>
+        <v>570</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>572</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>350</v>
+        <v>274</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>571</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>538</v>
+        <v>428</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>465</v>
       </c>
       <c r="J34" s="9">
-        <v>9</v>
-      </c>
-      <c r="K34" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="K34" s="16"/>
       <c r="U34" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="24.75" thickBot="1">
+    <row r="35" spans="1:21" ht="36.75" thickBot="1">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
-        <f>ROW(B35) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>434</v>
+      <c r="C35" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>433</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="J35" s="7">
-        <v>1</v>
-      </c>
-      <c r="K35" s="7"/>
+      <c r="J35" s="9">
+        <v>9</v>
+      </c>
+      <c r="K35" s="9"/>
       <c r="U35" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="15.75" thickBot="1">
+    <row r="36" spans="1:21" ht="24.75" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J36" s="14">
-        <v>1</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="D36" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J36" s="7">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7"/>
       <c r="U36" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3591,214 +3598,216 @@
     <row r="37" spans="1:21" ht="15.75" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
-        <f>ROW(B37) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="J37" s="7">
-        <v>2</v>
-      </c>
-      <c r="K37" s="7"/>
+      <c r="C37" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J37" s="14">
+        <v>1</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U37" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="36.75" thickBot="1">
+    <row r="38" spans="1:21" ht="15.75" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B38) - ROW($B$2)</f>
         <v>36</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>184</v>
+      <c r="C38" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="G38" s="10">
-        <v>5027740891</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>436</v>
+        <v>282</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>428</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J38" s="9">
-        <v>1</v>
-      </c>
-      <c r="K38" s="9"/>
+      <c r="J38" s="7">
+        <v>2</v>
+      </c>
+      <c r="K38" s="7"/>
       <c r="U38" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="48.75" thickBot="1">
+    <row r="39" spans="1:21" ht="36.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
-        <f>ROW(B39) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>185</v>
+      <c r="C39" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>184</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>437</v>
+      <c r="G39" s="10">
+        <v>5027740891</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>436</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J39" s="7">
-        <v>1</v>
-      </c>
-      <c r="K39" s="7"/>
+      <c r="J39" s="9">
+        <v>1</v>
+      </c>
+      <c r="K39" s="9"/>
       <c r="U39" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="24.75" thickBot="1">
+    <row r="40" spans="1:21" ht="48.75" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B40) - ROW($B$2)</f>
         <v>38</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>186</v>
+      <c r="C40" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>438</v>
+      <c r="G40" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J40" s="9">
-        <v>1</v>
-      </c>
-      <c r="K40" s="9"/>
+      <c r="J40" s="7">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7"/>
       <c r="U40" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="15.75" thickBot="1">
+    <row r="41" spans="1:21" ht="24.75" thickBot="1">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
-        <f>ROW(B41) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>187</v>
+      <c r="C41" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G41" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>439</v>
+      <c r="G41" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>438</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J41" s="7">
-        <v>1</v>
-      </c>
-      <c r="K41" s="7"/>
+      <c r="J41" s="9">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9"/>
       <c r="U41" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="26.25" thickBot="1">
+    <row r="42" spans="1:21" ht="15.75" thickBot="1">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B42) - ROW($B$2)</f>
         <v>40</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>188</v>
+      <c r="C42" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="H42" s="9" t="s">
+      <c r="G42" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>439</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J42" s="9">
-        <v>2</v>
-      </c>
-      <c r="K42" s="9"/>
+      <c r="J42" s="7">
+        <v>1</v>
+      </c>
+      <c r="K42" s="7"/>
       <c r="U42" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3813,30 +3822,28 @@
       <c r="C43" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="15" t="s">
+      <c r="D43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="I43" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J43" s="14">
-        <v>1</v>
-      </c>
-      <c r="K43" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="I43" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="J43" s="9">
+        <v>2</v>
+      </c>
+      <c r="K43" s="9"/>
       <c r="U43" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3849,61 +3856,63 @@
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F44" s="14" t="s">
         <v>537</v>
       </c>
-      <c r="G44" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="J44" s="9">
-        <v>1</v>
-      </c>
-      <c r="K44" s="9"/>
+      <c r="G44" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J44" s="14">
+        <v>1</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U44" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="15.75" thickBot="1">
+    <row r="45" spans="1:21" ht="26.25" thickBot="1">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>537</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>354</v>
+        <v>287</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="J45" s="9">
         <v>1</v>
@@ -3914,183 +3923,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="24.75" thickBot="1">
+    <row r="46" spans="1:21" ht="15.75" thickBot="1">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f>ROW(B46) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>191</v>
+      <c r="C46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="J46" s="7">
-        <v>3</v>
-      </c>
-      <c r="K46" s="7"/>
+      <c r="G46" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="J46" s="9">
+        <v>1</v>
+      </c>
+      <c r="K46" s="9"/>
       <c r="U46" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="15.75" thickBot="1">
+    <row r="47" spans="1:21" ht="24.75" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>192</v>
+      <c r="D47" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="I47" s="10" t="s">
+      <c r="G47" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="I47" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="J47" s="9">
-        <v>1</v>
-      </c>
-      <c r="K47" s="9"/>
+      <c r="J47" s="7">
+        <v>3</v>
+      </c>
+      <c r="K47" s="7"/>
       <c r="U47" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="24.75" thickBot="1">
+    <row r="48" spans="1:21" ht="15.75" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f>ROW(B48) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>193</v>
+      <c r="D48" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G48" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="J48" s="7">
-        <v>1</v>
-      </c>
-      <c r="K48" s="7"/>
+      <c r="G48" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="J48" s="9">
+        <v>1</v>
+      </c>
+      <c r="K48" s="9"/>
       <c r="U48" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="15.75" thickBot="1">
+    <row r="49" spans="1:21" ht="24.75" thickBot="1">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="F49" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="G49" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J49" s="14">
-        <v>1</v>
-      </c>
-      <c r="K49" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="C49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="J49" s="7">
+        <v>1</v>
+      </c>
+      <c r="K49" s="7"/>
       <c r="U49" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="24.75" thickBot="1">
+    <row r="50" spans="1:21" ht="15.75" thickBot="1">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f>ROW(B50) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="J50" s="7">
-        <v>1</v>
-      </c>
-      <c r="K50" s="7"/>
+      <c r="C50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J50" s="14">
+        <v>1</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U50" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4099,34 +4108,34 @@
     <row r="51" spans="1:21" ht="24.75" thickBot="1">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>446</v>
+      <c r="D51" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>445</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J51" s="9">
-        <v>5</v>
-      </c>
-      <c r="K51" s="9"/>
+      <c r="J51" s="7">
+        <v>1</v>
+      </c>
+      <c r="K51" s="7"/>
       <c r="U51" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4135,178 +4144,178 @@
     <row r="52" spans="1:21" ht="24.75" thickBot="1">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f>ROW(B52) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>447</v>
+      <c r="D52" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J52" s="7">
-        <v>2</v>
-      </c>
-      <c r="K52" s="7"/>
+      <c r="J52" s="9">
+        <v>5</v>
+      </c>
+      <c r="K52" s="9"/>
       <c r="U52" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="15.75" thickBot="1">
+    <row r="53" spans="1:21" ht="24.75" thickBot="1">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="H53" s="9" t="s">
+      <c r="D53" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>447</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J53" s="9">
-        <v>1</v>
-      </c>
-      <c r="K53" s="9"/>
+      <c r="J53" s="7">
+        <v>2</v>
+      </c>
+      <c r="K53" s="7"/>
       <c r="U53" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="24.75" thickBot="1">
+    <row r="54" spans="1:21" ht="15.75" thickBot="1">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f>ROW(B54) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>446</v>
+      <c r="D54" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>447</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J54" s="7">
-        <v>1</v>
-      </c>
-      <c r="K54" s="7"/>
+      <c r="J54" s="9">
+        <v>1</v>
+      </c>
+      <c r="K54" s="9"/>
       <c r="U54" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="36.75" thickBot="1">
+    <row r="55" spans="1:21" ht="24.75" thickBot="1">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>448</v>
+      <c r="C55" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>446</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J55" s="9">
-        <v>1</v>
-      </c>
-      <c r="K55" s="9"/>
+      <c r="J55" s="7">
+        <v>1</v>
+      </c>
+      <c r="K55" s="7"/>
       <c r="U55" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="15.75" thickBot="1">
+    <row r="56" spans="1:21" ht="36.75" thickBot="1">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f>ROW(B56) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>435</v>
+      <c r="C56" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>448</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J56" s="7">
-        <v>1</v>
-      </c>
-      <c r="K56" s="7"/>
+      <c r="J56" s="9">
+        <v>1</v>
+      </c>
+      <c r="K56" s="9"/>
       <c r="U56" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4315,34 +4324,34 @@
     <row r="57" spans="1:21" ht="15.75" thickBot="1">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B57) - ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>449</v>
+      <c r="D57" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>435</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J57" s="9">
-        <v>6</v>
-      </c>
-      <c r="K57" s="9"/>
+      <c r="J57" s="7">
+        <v>1</v>
+      </c>
+      <c r="K57" s="7"/>
       <c r="U57" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4351,34 +4360,34 @@
     <row r="58" spans="1:21" ht="15.75" thickBot="1">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
-        <f>ROW(B58) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>431</v>
+      <c r="C58" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="J58" s="7">
-        <v>7</v>
-      </c>
-      <c r="K58" s="7"/>
+        <v>538</v>
+      </c>
+      <c r="J58" s="9">
+        <v>6</v>
+      </c>
+      <c r="K58" s="9"/>
       <c r="U58" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4387,34 +4396,34 @@
     <row r="59" spans="1:21" ht="15.75" thickBot="1">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F59" s="9" t="s">
+      <c r="D59" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H59" s="9" t="s">
+      <c r="G59" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="H59" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I59" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="J59" s="9">
-        <v>1</v>
-      </c>
-      <c r="K59" s="9"/>
+      <c r="I59" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="J59" s="7">
+        <v>7</v>
+      </c>
+      <c r="K59" s="7"/>
       <c r="U59" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4423,34 +4432,34 @@
     <row r="60" spans="1:21" ht="15.75" thickBot="1">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
-        <f>ROW(B60) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G60" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="H60" s="7" t="s">
+      <c r="G60" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H60" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I60" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="J60" s="7">
-        <v>1</v>
-      </c>
-      <c r="K60" s="7"/>
+      <c r="I60" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="J60" s="9">
+        <v>1</v>
+      </c>
+      <c r="K60" s="9"/>
       <c r="U60" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4459,34 +4468,34 @@
     <row r="61" spans="1:21" ht="15.75" thickBot="1">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B61) - ROW($B$2)</f>
         <v>59</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F61" s="9" t="s">
+      <c r="C61" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G61" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H61" s="9" t="s">
+      <c r="G61" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H61" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I61" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="J61" s="9">
-        <v>1</v>
-      </c>
-      <c r="K61" s="9"/>
+      <c r="I61" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="J61" s="7">
+        <v>1</v>
+      </c>
+      <c r="K61" s="7"/>
       <c r="U61" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4495,34 +4504,34 @@
     <row r="62" spans="1:21" ht="15.75" thickBot="1">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
-        <f>ROW(B62) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F62" s="7" t="s">
+      <c r="C62" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="H62" s="7" t="s">
+      <c r="G62" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H62" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I62" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="J62" s="7">
-        <v>1</v>
-      </c>
-      <c r="K62" s="7"/>
+      <c r="I62" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="J62" s="9">
+        <v>1</v>
+      </c>
+      <c r="K62" s="9"/>
       <c r="U62" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4531,34 +4540,34 @@
     <row r="63" spans="1:21" ht="15.75" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B63) - ROW($B$2)</f>
         <v>61</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="H63" s="9" t="s">
+      <c r="C63" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I63" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="J63" s="9">
-        <v>1</v>
-      </c>
-      <c r="K63" s="9"/>
+      <c r="I63" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="J63" s="7">
+        <v>1</v>
+      </c>
+      <c r="K63" s="7"/>
       <c r="U63" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4567,34 +4576,34 @@
     <row r="64" spans="1:21" ht="15.75" thickBot="1">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
-        <f>ROW(B64) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C64" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="H64" s="7" t="s">
+      <c r="C64" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H64" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I64" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="J64" s="7">
-        <v>1</v>
-      </c>
-      <c r="K64" s="7"/>
+      <c r="I64" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="J64" s="9">
+        <v>1</v>
+      </c>
+      <c r="K64" s="9"/>
       <c r="U64" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4603,34 +4612,34 @@
     <row r="65" spans="1:21" ht="15.75" thickBot="1">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B65) - ROW($B$2)</f>
         <v>63</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F65" s="9" t="s">
+      <c r="C65" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G65" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="H65" s="9" t="s">
+      <c r="G65" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H65" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I65" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="J65" s="9">
-        <v>1</v>
-      </c>
-      <c r="K65" s="9"/>
+      <c r="I65" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="J65" s="7">
+        <v>1</v>
+      </c>
+      <c r="K65" s="7"/>
       <c r="U65" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4639,34 +4648,34 @@
     <row r="66" spans="1:21" ht="15.75" thickBot="1">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
-        <f>ROW(B66) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F66" s="7" t="s">
+      <c r="D66" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="H66" s="7" t="s">
+      <c r="G66" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H66" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I66" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="J66" s="7">
-        <v>1</v>
-      </c>
-      <c r="K66" s="7"/>
+      <c r="I66" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="J66" s="9">
+        <v>1</v>
+      </c>
+      <c r="K66" s="9"/>
       <c r="U66" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4675,34 +4684,34 @@
     <row r="67" spans="1:21" ht="15.75" thickBot="1">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B67) - ROW($B$2)</f>
         <v>65</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F67" s="9" t="s">
+      <c r="D67" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F67" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H67" s="9" t="s">
+      <c r="G67" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H67" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I67" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="J67" s="9">
-        <v>1</v>
-      </c>
-      <c r="K67" s="9"/>
+      <c r="I67" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="J67" s="7">
+        <v>1</v>
+      </c>
+      <c r="K67" s="7"/>
       <c r="U67" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4711,178 +4720,178 @@
     <row r="68" spans="1:21" ht="15.75" thickBot="1">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
-        <f>ROW(B68) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="F68" s="7" t="s">
+      <c r="D68" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G68" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H68" s="7" t="s">
+      <c r="G68" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H68" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I68" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="J68" s="7">
-        <v>1</v>
-      </c>
-      <c r="K68" s="7"/>
+      <c r="I68" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="J68" s="9">
+        <v>1</v>
+      </c>
+      <c r="K68" s="9"/>
       <c r="U68" t="b">
-        <f t="shared" ref="U68:U131" si="2">IF(P68=J68,TRUE,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="15.75" thickBot="1">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B69) - ROW($B$2)</f>
         <v>67</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F69" s="9" t="s">
+      <c r="D69" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F69" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="H69" s="9" t="s">
+      <c r="G69" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H69" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I69" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="J69" s="9">
-        <v>6</v>
-      </c>
-      <c r="K69" s="9"/>
+      <c r="I69" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="J69" s="7">
+        <v>1</v>
+      </c>
+      <c r="K69" s="7"/>
       <c r="U69" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="U69:U132" si="2">IF(P69=J69,TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:21" ht="15.75" thickBot="1">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
-        <f>ROW(B70) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="H70" s="7" t="s">
+      <c r="D70" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H70" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I70" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="J70" s="7">
-        <v>1</v>
-      </c>
-      <c r="K70" s="7"/>
+      <c r="I70" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="J70" s="9">
+        <v>6</v>
+      </c>
+      <c r="K70" s="9"/>
       <c r="U70" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="36.75" thickBot="1">
+    <row r="71" spans="1:21" ht="15.75" thickBot="1">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B71) - ROW($B$2)</f>
         <v>69</v>
       </c>
-      <c r="C71" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="H71" s="9" t="s">
+      <c r="C71" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="H71" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I71" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="J71" s="9">
-        <v>19</v>
-      </c>
-      <c r="K71" s="9"/>
+      <c r="I71" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="J71" s="7">
+        <v>1</v>
+      </c>
+      <c r="K71" s="7"/>
       <c r="U71" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="15.75" thickBot="1">
+    <row r="72" spans="1:21" ht="36.75" thickBot="1">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
-        <f>ROW(B72) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F72" s="7" t="s">
+      <c r="C72" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F72" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G72" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="H72" s="7" t="s">
+      <c r="G72" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="H72" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I72" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="J72" s="7">
-        <v>2</v>
-      </c>
-      <c r="K72" s="7"/>
+      <c r="I72" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="J72" s="9">
+        <v>19</v>
+      </c>
+      <c r="K72" s="9"/>
       <c r="U72" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4891,34 +4900,34 @@
     <row r="73" spans="1:21" ht="15.75" thickBot="1">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="F73" s="9" t="s">
+      <c r="C73" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G73" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="H73" s="9" t="s">
+      <c r="G73" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H73" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I73" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="J73" s="9">
-        <v>1</v>
-      </c>
-      <c r="K73" s="9"/>
+      <c r="I73" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="J73" s="7">
+        <v>2</v>
+      </c>
+      <c r="K73" s="7"/>
       <c r="U73" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4927,106 +4936,106 @@
     <row r="74" spans="1:21" ht="15.75" thickBot="1">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
-        <f>ROW(B74) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="F74" s="7" t="s">
+      <c r="C74" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G74" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="H74" s="7" t="s">
+      <c r="G74" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="H74" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I74" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="J74" s="7">
-        <v>1</v>
-      </c>
-      <c r="K74" s="7"/>
+      <c r="I74" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="J74" s="9">
+        <v>1</v>
+      </c>
+      <c r="K74" s="9"/>
       <c r="U74" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="24.75" thickBot="1">
+    <row r="75" spans="1:21" ht="15.75" thickBot="1">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B75) - ROW($B$2)</f>
         <v>73</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="H75" s="9" t="s">
+      <c r="D75" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="H75" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I75" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="J75" s="9">
-        <v>10</v>
-      </c>
-      <c r="K75" s="9"/>
+      <c r="I75" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="J75" s="7">
+        <v>1</v>
+      </c>
+      <c r="K75" s="7"/>
       <c r="U75" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="15.75" thickBot="1">
+    <row r="76" spans="1:21" ht="24.75" thickBot="1">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
-        <f>ROW(B76) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="F76" s="7" t="s">
+      <c r="C76" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F76" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G76" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="H76" s="7" t="s">
+      <c r="G76" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="H76" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I76" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="J76" s="7">
-        <v>1</v>
-      </c>
-      <c r="K76" s="7"/>
+      <c r="I76" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="J76" s="9">
+        <v>10</v>
+      </c>
+      <c r="K76" s="9"/>
       <c r="U76" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5035,34 +5044,34 @@
     <row r="77" spans="1:21" ht="15.75" thickBot="1">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B77) - ROW($B$2)</f>
         <v>75</v>
       </c>
-      <c r="C77" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="F77" s="9" t="s">
+      <c r="C77" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F77" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G77" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="H77" s="9" t="s">
+      <c r="G77" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="H77" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I77" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="J77" s="9">
-        <v>1</v>
-      </c>
-      <c r="K77" s="9"/>
+      <c r="I77" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="J77" s="7">
+        <v>1</v>
+      </c>
+      <c r="K77" s="7"/>
       <c r="U77" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5071,34 +5080,34 @@
     <row r="78" spans="1:21" ht="15.75" thickBot="1">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
-        <f>ROW(B78) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="F78" s="7" t="s">
+      <c r="C78" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F78" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G78" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="H78" s="7" t="s">
+      <c r="G78" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="H78" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I78" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="J78" s="7">
-        <v>1</v>
-      </c>
-      <c r="K78" s="7"/>
+      <c r="I78" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="J78" s="9">
+        <v>1</v>
+      </c>
+      <c r="K78" s="9"/>
       <c r="U78" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5107,34 +5116,34 @@
     <row r="79" spans="1:21" ht="15.75" thickBot="1">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B79) - ROW($B$2)</f>
         <v>77</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="F79" s="9" t="s">
+      <c r="D79" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G79" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H79" s="9" t="s">
+      <c r="G79" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="H79" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I79" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="J79" s="9">
-        <v>1</v>
-      </c>
-      <c r="K79" s="9"/>
+      <c r="I79" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="J79" s="7">
+        <v>1</v>
+      </c>
+      <c r="K79" s="7"/>
       <c r="U79" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5143,34 +5152,34 @@
     <row r="80" spans="1:21" ht="15.75" thickBot="1">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
-        <f>ROW(B80) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D80" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F80" s="7" t="s">
+      <c r="D80" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F80" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G80" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="H80" s="7" t="s">
+      <c r="G80" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="H80" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I80" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="J80" s="7">
-        <v>1</v>
-      </c>
-      <c r="K80" s="7"/>
+      <c r="I80" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="J80" s="9">
+        <v>1</v>
+      </c>
+      <c r="K80" s="9"/>
       <c r="U80" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5179,34 +5188,34 @@
     <row r="81" spans="1:21" ht="15.75" thickBot="1">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B81) - ROW($B$2)</f>
         <v>79</v>
       </c>
-      <c r="C81" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F81" s="9" t="s">
+      <c r="C81" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G81" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="H81" s="9" t="s">
+      <c r="G81" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="H81" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I81" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="J81" s="9">
-        <v>7</v>
-      </c>
-      <c r="K81" s="9"/>
+      <c r="I81" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="J81" s="7">
+        <v>1</v>
+      </c>
+      <c r="K81" s="7"/>
       <c r="U81" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5215,34 +5224,34 @@
     <row r="82" spans="1:21" ht="15.75" thickBot="1">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
-        <f>ROW(B82) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="F82" s="7" t="s">
+      <c r="D82" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F82" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G82" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="H82" s="7" t="s">
+      <c r="G82" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H82" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I82" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="J82" s="7">
-        <v>4</v>
-      </c>
-      <c r="K82" s="7"/>
+      <c r="I82" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="J82" s="9">
+        <v>7</v>
+      </c>
+      <c r="K82" s="9"/>
       <c r="U82" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5251,34 +5260,34 @@
     <row r="83" spans="1:21" ht="15.75" thickBot="1">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B83) - ROW($B$2)</f>
         <v>81</v>
       </c>
-      <c r="C83" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F83" s="9" t="s">
+      <c r="C83" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F83" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G83" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H83" s="9" t="s">
+      <c r="G83" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="H83" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I83" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="J83" s="9">
-        <v>5</v>
-      </c>
-      <c r="K83" s="9"/>
+      <c r="I83" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="J83" s="7">
+        <v>4</v>
+      </c>
+      <c r="K83" s="7"/>
       <c r="U83" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5287,34 +5296,34 @@
     <row r="84" spans="1:21" ht="15.75" thickBot="1">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
-        <f>ROW(B84) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D84" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F84" s="7" t="s">
+      <c r="D84" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F84" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="H84" s="7" t="s">
+      <c r="G84" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H84" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I84" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="J84" s="7">
-        <v>1</v>
-      </c>
-      <c r="K84" s="7"/>
+      <c r="I84" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="J84" s="9">
+        <v>5</v>
+      </c>
+      <c r="K84" s="9"/>
       <c r="U84" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5323,34 +5332,34 @@
     <row r="85" spans="1:21" ht="15.75" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B85) - ROW($B$2)</f>
         <v>83</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F85" s="9" t="s">
+      <c r="D85" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G85" s="10" t="s">
-        <v>535</v>
+      <c r="G85" s="8" t="s">
+        <v>389</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I85" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="J85" s="9">
-        <v>2</v>
-      </c>
-      <c r="K85" s="9"/>
+      <c r="I85" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="J85" s="7">
+        <v>1</v>
+      </c>
+      <c r="K85" s="7"/>
       <c r="U85" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5359,34 +5368,34 @@
     <row r="86" spans="1:21" ht="15.75" thickBot="1">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
-        <f>ROW(B86) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="F86" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F86" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G86" s="8" t="s">
-        <v>390</v>
+      <c r="G86" s="10" t="s">
+        <v>535</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I86" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="J86" s="7">
-        <v>1</v>
-      </c>
-      <c r="K86" s="7"/>
+      <c r="I86" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="J86" s="9">
+        <v>2</v>
+      </c>
+      <c r="K86" s="9"/>
       <c r="U86" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5395,34 +5404,34 @@
     <row r="87" spans="1:21" ht="15.75" thickBot="1">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B87) - ROW($B$2)</f>
         <v>85</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F87" s="9" t="s">
+      <c r="D87" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G87" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="H87" s="9" t="s">
+      <c r="G87" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H87" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I87" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="J87" s="9">
-        <v>1</v>
-      </c>
-      <c r="K87" s="9"/>
+      <c r="I87" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="J87" s="7">
+        <v>1</v>
+      </c>
+      <c r="K87" s="7"/>
       <c r="U87" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5431,34 +5440,34 @@
     <row r="88" spans="1:21" ht="15.75" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
-        <f>ROW(B88) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="F88" s="7" t="s">
+      <c r="C88" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F88" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G88" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="H88" s="7" t="s">
+      <c r="G88" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="H88" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I88" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="J88" s="7">
-        <v>1</v>
-      </c>
-      <c r="K88" s="7"/>
+      <c r="I88" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="J88" s="9">
+        <v>1</v>
+      </c>
+      <c r="K88" s="9"/>
       <c r="U88" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5467,34 +5476,34 @@
     <row r="89" spans="1:21" ht="15.75" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B89) - ROW($B$2)</f>
         <v>87</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="H89" s="9" t="s">
+      <c r="D89" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="H89" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I89" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="J89" s="9">
-        <v>1</v>
-      </c>
-      <c r="K89" s="9"/>
+      <c r="I89" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="J89" s="7">
+        <v>1</v>
+      </c>
+      <c r="K89" s="7"/>
       <c r="U89" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5503,34 +5512,34 @@
     <row r="90" spans="1:21" ht="15.75" thickBot="1">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
-        <f>ROW(B90) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D90" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F90" s="7" t="s">
+      <c r="D90" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F90" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="G90" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H90" s="7" t="s">
+      <c r="G90" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="H90" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I90" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="J90" s="7">
-        <v>1</v>
-      </c>
-      <c r="K90" s="7"/>
+      <c r="I90" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="J90" s="9">
+        <v>1</v>
+      </c>
+      <c r="K90" s="9"/>
       <c r="U90" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5539,34 +5548,34 @@
     <row r="91" spans="1:21" ht="15.75" thickBot="1">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B91) - ROW($B$2)</f>
         <v>89</v>
       </c>
-      <c r="C91" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H91" s="9" t="s">
+      <c r="C91" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I91" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="J91" s="9">
-        <v>1</v>
-      </c>
-      <c r="K91" s="9"/>
+      <c r="I91" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="J91" s="7">
+        <v>1</v>
+      </c>
+      <c r="K91" s="7"/>
       <c r="U91" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5575,34 +5584,34 @@
     <row r="92" spans="1:21" ht="15.75" thickBot="1">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
-        <f>ROW(B92) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F92" s="7" t="s">
+      <c r="C92" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F92" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G92" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H92" s="7" t="s">
+      <c r="G92" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="H92" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I92" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="J92" s="7">
-        <v>3</v>
-      </c>
-      <c r="K92" s="7"/>
+      <c r="I92" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="J92" s="9">
+        <v>1</v>
+      </c>
+      <c r="K92" s="9"/>
       <c r="U92" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5611,34 +5620,34 @@
     <row r="93" spans="1:21" ht="15.75" thickBot="1">
       <c r="A93" s="1"/>
       <c r="B93" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B93) - ROW($B$2)</f>
         <v>91</v>
       </c>
-      <c r="C93" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F93" s="9" t="s">
+      <c r="C93" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F93" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G93" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="H93" s="9" t="s">
+      <c r="G93" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="H93" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I93" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="J93" s="9">
-        <v>6</v>
-      </c>
-      <c r="K93" s="9"/>
+      <c r="I93" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="J93" s="7">
+        <v>3</v>
+      </c>
+      <c r="K93" s="7"/>
       <c r="U93" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5647,34 +5656,34 @@
     <row r="94" spans="1:21" ht="15.75" thickBot="1">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
-        <f>ROW(B94) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F94" s="7" t="s">
+      <c r="D94" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F94" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G94" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="H94" s="7" t="s">
+      <c r="G94" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="H94" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I94" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="J94" s="7">
-        <v>1</v>
-      </c>
-      <c r="K94" s="7"/>
+      <c r="I94" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="J94" s="9">
+        <v>6</v>
+      </c>
+      <c r="K94" s="9"/>
       <c r="U94" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5683,34 +5692,34 @@
     <row r="95" spans="1:21" ht="15.75" thickBot="1">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B95) - ROW($B$2)</f>
         <v>93</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F95" s="9" t="s">
+      <c r="D95" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F95" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G95" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="H95" s="9" t="s">
+      <c r="G95" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H95" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I95" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="J95" s="9">
-        <v>1</v>
-      </c>
-      <c r="K95" s="9"/>
+      <c r="I95" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="J95" s="7">
+        <v>1</v>
+      </c>
+      <c r="K95" s="7"/>
       <c r="U95" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5719,34 +5728,34 @@
     <row r="96" spans="1:21" ht="15.75" thickBot="1">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
-        <f>ROW(B96) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="F96" s="7" t="s">
+      <c r="D96" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F96" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G96" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="H96" s="7" t="s">
+      <c r="G96" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="H96" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I96" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="J96" s="7">
-        <v>1</v>
-      </c>
-      <c r="K96" s="7"/>
+      <c r="I96" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="J96" s="9">
+        <v>1</v>
+      </c>
+      <c r="K96" s="9"/>
       <c r="U96" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5755,34 +5764,34 @@
     <row r="97" spans="1:21" ht="15.75" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B97) - ROW($B$2)</f>
         <v>95</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="F97" s="9" t="s">
+      <c r="D97" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F97" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G97" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="H97" s="9" t="s">
+      <c r="G97" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H97" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I97" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="J97" s="9">
-        <v>2</v>
-      </c>
-      <c r="K97" s="9"/>
+      <c r="I97" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="J97" s="7">
+        <v>1</v>
+      </c>
+      <c r="K97" s="7"/>
       <c r="U97" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5791,36 +5800,34 @@
     <row r="98" spans="1:21" ht="15.75" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
-        <f>ROW(B98) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D98" s="14" t="s">
-        <v>564</v>
-      </c>
-      <c r="E98" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="F98" s="14" t="s">
+      <c r="D98" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F98" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G98" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="H98" s="14" t="s">
+      <c r="G98" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H98" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I98" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J98" s="14">
+      <c r="I98" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="J98" s="9">
         <v>2</v>
       </c>
-      <c r="K98" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="K98" s="9"/>
       <c r="U98" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5832,20 +5839,20 @@
         <f>ROW(B99) - ROW($B$2)</f>
         <v>97</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F99" s="14" t="s">
         <v>299</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H99" s="14" t="s">
         <v>431</v>
@@ -5854,7 +5861,7 @@
         <v>485</v>
       </c>
       <c r="J99" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" s="16" t="s">
         <v>536</v>
@@ -5864,73 +5871,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="36.75" thickBot="1">
+    <row r="100" spans="1:21" ht="15.75" thickBot="1">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B100) - ROW($B$2)</f>
         <v>98</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="H100" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="H100" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="I100" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="J100" s="9">
-        <v>1</v>
-      </c>
-      <c r="K100" s="9"/>
+      <c r="I100" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J100" s="14">
+        <v>1</v>
+      </c>
+      <c r="K100" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U100" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="15.75" thickBot="1">
+    <row r="101" spans="1:21" ht="36.75" thickBot="1">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
-        <f>ROW(B101) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D101" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="H101" s="7" t="s">
+      <c r="D101" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I101" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="J101" s="7">
-        <v>1</v>
-      </c>
-      <c r="K101" s="7"/>
+      <c r="I101" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J101" s="9">
+        <v>1</v>
+      </c>
+      <c r="K101" s="9"/>
       <c r="U101" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5939,34 +5948,34 @@
     <row r="102" spans="1:21" ht="15.75" thickBot="1">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B102) - ROW($B$2)</f>
         <v>100</v>
       </c>
-      <c r="C102" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F102" s="9" t="s">
+      <c r="C102" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F102" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G102" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="H102" s="9" t="s">
+      <c r="G102" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="H102" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I102" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="J102" s="9">
-        <v>1</v>
-      </c>
-      <c r="K102" s="9"/>
+      <c r="I102" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J102" s="7">
+        <v>1</v>
+      </c>
+      <c r="K102" s="7"/>
       <c r="U102" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5975,34 +5984,34 @@
     <row r="103" spans="1:21" ht="15.75" thickBot="1">
       <c r="A103" s="1"/>
       <c r="B103" s="11">
-        <f>ROW(B103) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D103" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F103" s="7" t="s">
+      <c r="D103" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F103" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G103" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="H103" s="7" t="s">
+      <c r="G103" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I103" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="J103" s="7">
-        <v>1</v>
-      </c>
-      <c r="K103" s="7"/>
+      <c r="I103" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="J103" s="9">
+        <v>1</v>
+      </c>
+      <c r="K103" s="9"/>
       <c r="U103" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6011,36 +6020,34 @@
     <row r="104" spans="1:21" ht="15.75" thickBot="1">
       <c r="A104" s="1"/>
       <c r="B104" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B104) - ROW($B$2)</f>
         <v>102</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D104" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E104" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="F104" s="14" t="s">
+      <c r="D104" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F104" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G104" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="H104" s="14" t="s">
+      <c r="G104" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="H104" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I104" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J104" s="14">
-        <v>1</v>
-      </c>
-      <c r="K104" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="I104" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="J104" s="7">
+        <v>1</v>
+      </c>
+      <c r="K104" s="7"/>
       <c r="U104" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6049,34 +6056,36 @@
     <row r="105" spans="1:21" ht="15.75" thickBot="1">
       <c r="A105" s="1"/>
       <c r="B105" s="11">
-        <f>ROW(B105) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="F105" s="7" t="s">
+      <c r="C105" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F105" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="G105" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H105" s="7" t="s">
+      <c r="G105" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="H105" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="I105" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="J105" s="7">
-        <v>1</v>
-      </c>
-      <c r="K105" s="7"/>
+      <c r="I105" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J105" s="14">
+        <v>1</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U105" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6085,36 +6094,34 @@
     <row r="106" spans="1:21" ht="15.75" thickBot="1">
       <c r="A106" s="1"/>
       <c r="B106" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B106) - ROW($B$2)</f>
         <v>104</v>
       </c>
-      <c r="C106" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E106" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="F106" s="14" t="s">
+      <c r="C106" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F106" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G106" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="H106" s="14" t="s">
+      <c r="G106" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H106" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I106" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J106" s="14">
-        <v>1</v>
-      </c>
-      <c r="K106" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="I106" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="J106" s="7">
+        <v>1</v>
+      </c>
+      <c r="K106" s="7"/>
       <c r="U106" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6123,34 +6130,36 @@
     <row r="107" spans="1:21" ht="15.75" thickBot="1">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
-        <f>ROW(B107) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D107" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="F107" s="7" t="s">
+      <c r="D107" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F107" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="G107" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="H107" s="7" t="s">
+      <c r="G107" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="H107" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="I107" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="J107" s="7">
-        <v>4</v>
-      </c>
-      <c r="K107" s="7"/>
+      <c r="I107" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J107" s="14">
+        <v>1</v>
+      </c>
+      <c r="K107" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U107" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6159,34 +6168,34 @@
     <row r="108" spans="1:21" ht="15.75" thickBot="1">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B108) - ROW($B$2)</f>
         <v>106</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="F108" s="9" t="s">
+      <c r="D108" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="F108" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G108" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="H108" s="9" t="s">
+      <c r="G108" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="H108" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="I108" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="J108" s="9">
-        <v>1</v>
-      </c>
-      <c r="K108" s="9"/>
+      <c r="I108" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="J108" s="7">
+        <v>4</v>
+      </c>
+      <c r="K108" s="7"/>
       <c r="U108" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6195,36 +6204,34 @@
     <row r="109" spans="1:21" ht="15.75" thickBot="1">
       <c r="A109" s="1"/>
       <c r="B109" s="11">
-        <f>ROW(B109) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D109" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E109" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="F109" s="14" t="s">
+      <c r="D109" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F109" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="G109" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="H109" s="14" t="s">
+      <c r="G109" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="I109" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="J109" s="14">
-        <v>1</v>
-      </c>
-      <c r="K109" s="16" t="s">
-        <v>536</v>
-      </c>
+      <c r="I109" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="J109" s="9">
+        <v>1</v>
+      </c>
+      <c r="K109" s="9"/>
       <c r="U109" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6233,23 +6240,23 @@
     <row r="110" spans="1:21" ht="15.75" thickBot="1">
       <c r="A110" s="1"/>
       <c r="B110" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B110) - ROW($B$2)</f>
         <v>108</v>
       </c>
-      <c r="C110" s="13" t="s">
-        <v>19</v>
+      <c r="C110" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="H110" s="14" t="s">
         <v>431</v>
@@ -6258,7 +6265,7 @@
         <v>485</v>
       </c>
       <c r="J110" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K110" s="16" t="s">
         <v>536</v>
@@ -6277,208 +6284,210 @@
       <c r="C111" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D111" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F111" s="9" t="s">
+      <c r="D111" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F111" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="G111" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="H111" s="9" t="s">
+      <c r="G111" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="H111" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="I111" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="J111" s="9">
-        <v>1</v>
-      </c>
-      <c r="K111" s="9"/>
+      <c r="I111" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="J111" s="14">
+        <v>2</v>
+      </c>
+      <c r="K111" s="16" t="s">
+        <v>536</v>
+      </c>
       <c r="U111" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="24.75" thickBot="1">
+    <row r="112" spans="1:21" ht="15.75" thickBot="1">
       <c r="A112" s="1"/>
       <c r="B112" s="11">
-        <f>ROW(B112) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="C112" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="J112" s="7">
-        <v>1</v>
-      </c>
-      <c r="K112" s="7"/>
+      <c r="C112" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="J112" s="9">
+        <v>1</v>
+      </c>
+      <c r="K112" s="9"/>
       <c r="U112" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="48.75" thickBot="1">
+    <row r="113" spans="1:21" ht="24.75" thickBot="1">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B113) - ROW($B$2)</f>
         <v>111</v>
       </c>
-      <c r="C113" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>252</v>
+      <c r="C113" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G113" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>451</v>
+      <c r="G113" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>450</v>
       </c>
       <c r="I113" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J113" s="9">
-        <v>1</v>
-      </c>
-      <c r="K113" s="9"/>
+      <c r="J113" s="7">
+        <v>1</v>
+      </c>
+      <c r="K113" s="7"/>
       <c r="U113" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="36.75" thickBot="1">
+    <row r="114" spans="1:21" ht="48.75" thickBot="1">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
-        <f>ROW(B114) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>253</v>
+      <c r="D114" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G114" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="H114" s="7" t="s">
+      <c r="G114" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="H114" s="9" t="s">
         <v>451</v>
       </c>
       <c r="I114" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J114" s="7">
-        <v>4</v>
-      </c>
-      <c r="K114" s="7"/>
+      <c r="J114" s="9">
+        <v>1</v>
+      </c>
+      <c r="K114" s="9"/>
       <c r="U114" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="24.75" thickBot="1">
+    <row r="115" spans="1:21" ht="36.75" thickBot="1">
       <c r="A115" s="1"/>
       <c r="B115" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B115) - ROW($B$2)</f>
         <v>113</v>
       </c>
-      <c r="C115" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>452</v>
+      <c r="C115" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>451</v>
       </c>
       <c r="I115" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J115" s="9">
-        <v>1</v>
-      </c>
-      <c r="K115" s="9"/>
+      <c r="J115" s="7">
+        <v>4</v>
+      </c>
+      <c r="K115" s="7"/>
       <c r="U115" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="15.75" thickBot="1">
+    <row r="116" spans="1:21" ht="24.75" thickBot="1">
       <c r="A116" s="1"/>
       <c r="B116" s="11">
-        <f>ROW(B116) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>453</v>
+      <c r="D116" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>452</v>
       </c>
       <c r="I116" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J116" s="7">
-        <v>1</v>
-      </c>
-      <c r="K116" s="7"/>
+      <c r="J116" s="9">
+        <v>1</v>
+      </c>
+      <c r="K116" s="9"/>
       <c r="U116" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6487,106 +6496,106 @@
     <row r="117" spans="1:21" ht="15.75" thickBot="1">
       <c r="A117" s="1"/>
       <c r="B117" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B117) - ROW($B$2)</f>
         <v>115</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F117" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G117" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>454</v>
+      <c r="D117" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="I117" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J117" s="9">
-        <v>1</v>
-      </c>
-      <c r="K117" s="9"/>
+      <c r="J117" s="7">
+        <v>1</v>
+      </c>
+      <c r="K117" s="7"/>
       <c r="U117" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="24.75" thickBot="1">
+    <row r="118" spans="1:21" ht="15.75" thickBot="1">
       <c r="A118" s="1"/>
       <c r="B118" s="11">
-        <f>ROW(B118) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D118" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="G118" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>455</v>
+      <c r="D118" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>454</v>
       </c>
       <c r="I118" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J118" s="7">
-        <v>1</v>
-      </c>
-      <c r="K118" s="7"/>
+      <c r="J118" s="9">
+        <v>1</v>
+      </c>
+      <c r="K118" s="9"/>
       <c r="U118" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="15.75" thickBot="1">
+    <row r="119" spans="1:21" ht="24.75" thickBot="1">
       <c r="A119" s="1"/>
       <c r="B119" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B119) - ROW($B$2)</f>
         <v>117</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D119" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>456</v>
+      <c r="D119" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="I119" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J119" s="9">
-        <v>1</v>
-      </c>
-      <c r="K119" s="9"/>
+      <c r="J119" s="7">
+        <v>1</v>
+      </c>
+      <c r="K119" s="7"/>
       <c r="U119" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6595,34 +6604,34 @@
     <row r="120" spans="1:21" ht="15.75" thickBot="1">
       <c r="A120" s="1"/>
       <c r="B120" s="11">
-        <f>ROW(B120) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D120" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="H120" s="7" t="s">
+      <c r="D120" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="H120" s="9" t="s">
         <v>456</v>
       </c>
       <c r="I120" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J120" s="7">
-        <v>1</v>
-      </c>
-      <c r="K120" s="7"/>
+      <c r="J120" s="9">
+        <v>1</v>
+      </c>
+      <c r="K120" s="9"/>
       <c r="U120" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6631,34 +6640,34 @@
     <row r="121" spans="1:21" ht="15.75" thickBot="1">
       <c r="A121" s="1"/>
       <c r="B121" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B121) - ROW($B$2)</f>
         <v>119</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D121" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="H121" s="9" t="s">
+      <c r="D121" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>456</v>
       </c>
       <c r="I121" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J121" s="9">
-        <v>1</v>
-      </c>
-      <c r="K121" s="9"/>
+      <c r="J121" s="7">
+        <v>1</v>
+      </c>
+      <c r="K121" s="7"/>
       <c r="U121" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6667,34 +6676,34 @@
     <row r="122" spans="1:21" ht="15.75" thickBot="1">
       <c r="A122" s="1"/>
       <c r="B122" s="11">
-        <f>ROW(B122) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="H122" s="7" t="s">
+      <c r="D122" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="H122" s="9" t="s">
         <v>456</v>
       </c>
       <c r="I122" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J122" s="7">
-        <v>1</v>
-      </c>
-      <c r="K122" s="7"/>
+      <c r="J122" s="9">
+        <v>1</v>
+      </c>
+      <c r="K122" s="9"/>
       <c r="U122" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6703,34 +6712,34 @@
     <row r="123" spans="1:21" ht="15.75" thickBot="1">
       <c r="A123" s="1"/>
       <c r="B123" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B123) - ROW($B$2)</f>
         <v>121</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D123" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G123" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>457</v>
+      <c r="D123" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="I123" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J123" s="9">
-        <v>1</v>
-      </c>
-      <c r="K123" s="9"/>
+      <c r="J123" s="7">
+        <v>1</v>
+      </c>
+      <c r="K123" s="7"/>
       <c r="U123" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6739,70 +6748,70 @@
     <row r="124" spans="1:21" ht="15.75" thickBot="1">
       <c r="A124" s="1"/>
       <c r="B124" s="11">
-        <f>ROW(B124) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D124" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>456</v>
+      <c r="D124" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>457</v>
       </c>
       <c r="I124" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J124" s="7">
-        <v>1</v>
-      </c>
-      <c r="K124" s="7"/>
+      <c r="J124" s="9">
+        <v>1</v>
+      </c>
+      <c r="K124" s="9"/>
       <c r="U124" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="24.75" thickBot="1">
+    <row r="125" spans="1:21" ht="15.75" thickBot="1">
       <c r="A125" s="1"/>
       <c r="B125" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B125) - ROW($B$2)</f>
         <v>123</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C125" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D125" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>458</v>
+      <c r="D125" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="I125" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J125" s="9">
-        <v>1</v>
-      </c>
-      <c r="K125" s="9"/>
+      <c r="J125" s="7">
+        <v>1</v>
+      </c>
+      <c r="K125" s="7"/>
       <c r="U125" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6811,173 +6820,173 @@
     <row r="126" spans="1:21" ht="24.75" thickBot="1">
       <c r="A126" s="1"/>
       <c r="B126" s="11">
-        <f>ROW(B126) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="C126" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D126" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>456</v>
+      <c r="D126" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>458</v>
       </c>
       <c r="I126" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J126" s="7">
-        <v>1</v>
-      </c>
-      <c r="K126" s="7"/>
+      <c r="J126" s="9">
+        <v>1</v>
+      </c>
+      <c r="K126" s="9"/>
       <c r="U126" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="15.75" thickBot="1">
+    <row r="127" spans="1:21" ht="24.75" thickBot="1">
       <c r="A127" s="1"/>
       <c r="B127" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B127) - ROW($B$2)</f>
         <v>125</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D127" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="G127" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="H127" s="9" t="s">
+      <c r="D127" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H127" s="7" t="s">
         <v>456</v>
       </c>
       <c r="I127" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J127" s="9">
-        <v>1</v>
-      </c>
-      <c r="K127" s="9"/>
+      <c r="J127" s="7">
+        <v>1</v>
+      </c>
+      <c r="K127" s="7"/>
       <c r="U127" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="24.75" thickBot="1">
+    <row r="128" spans="1:21" ht="15.75" thickBot="1">
       <c r="A128" s="1"/>
       <c r="B128" s="11">
-        <f>ROW(B128) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D128" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>459</v>
+      <c r="D128" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>456</v>
       </c>
       <c r="I128" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J128" s="7">
-        <v>1</v>
-      </c>
-      <c r="K128" s="7"/>
+      <c r="J128" s="9">
+        <v>1</v>
+      </c>
+      <c r="K128" s="9"/>
       <c r="U128" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="15.75" thickBot="1">
+    <row r="129" spans="1:21" ht="24.75" thickBot="1">
       <c r="A129" s="1"/>
       <c r="B129" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B129) - ROW($B$2)</f>
         <v>127</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D129" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="G129" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>456</v>
+      <c r="D129" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>459</v>
       </c>
       <c r="I129" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J129" s="9">
-        <v>1</v>
-      </c>
-      <c r="K129" s="9"/>
+      <c r="J129" s="7">
+        <v>1</v>
+      </c>
+      <c r="K129" s="7"/>
       <c r="U129" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="36.75" thickBot="1">
+    <row r="130" spans="1:21" ht="15.75" thickBot="1">
       <c r="A130" s="1"/>
       <c r="B130" s="11">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="I130" s="10" t="s">
-        <v>530</v>
+        <v>456</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>538</v>
       </c>
       <c r="J130" s="9">
         <v>1</v>
@@ -6988,113 +6997,114 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="15.75" thickBot="1">
+    <row r="131" spans="1:21" ht="36.75" thickBot="1">
       <c r="A131" s="1"/>
       <c r="B131" s="11">
-        <f>ROW(B131) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="J131" s="7">
-        <v>2</v>
-      </c>
-      <c r="K131" s="7"/>
+      <c r="C131" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="J131" s="9">
+        <v>1</v>
+      </c>
+      <c r="K131" s="9"/>
       <c r="U131" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="36.75" thickBot="1">
+    <row r="132" spans="1:21" ht="15.75" thickBot="1">
+      <c r="A132" s="1"/>
       <c r="B132" s="11">
+        <f>ROW(B132) - ROW($B$2)</f>
+        <v>130</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="J132" s="7">
+        <v>2</v>
+      </c>
+      <c r="K132" s="7"/>
+      <c r="U132" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" ht="36.75" thickBot="1">
+      <c r="B133" s="11">
         <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="C132" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C133" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D132" s="9" t="s">
+      <c r="D133" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E132" s="10" t="s">
+      <c r="E133" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="F133" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="G132" s="10" t="s">
+      <c r="G133" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="H132" s="9" t="s">
+      <c r="H133" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="I132" s="10" t="s">
+      <c r="I133" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="J132" s="9">
-        <v>1</v>
-      </c>
-      <c r="K132" s="9"/>
-      <c r="U132" t="b">
-        <f t="shared" ref="U132:U138" si="3">IF(P132=J132,TRUE,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:21" ht="24.75" thickBot="1">
-      <c r="B133" s="11">
-        <f>ROW(B133) - ROW($B$2)</f>
-        <v>131</v>
-      </c>
-      <c r="C133" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="I133" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="J133" s="7">
-        <v>2</v>
-      </c>
-      <c r="K133" s="7"/>
+      <c r="J133" s="9">
+        <v>1</v>
+      </c>
+      <c r="K133" s="9"/>
       <c r="U133" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:21" ht="64.5" thickBot="1">
+        <f t="shared" ref="U133:U139" si="3">IF(P133=J133,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" ht="24.75" thickBot="1">
       <c r="B134" s="11">
         <f>ROW(B134) - ROW($B$2)</f>
         <v>132</v>
@@ -7106,34 +7116,32 @@
         <v>538</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="F134" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="F134" s="7" t="s">
         <v>537</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="I134" s="8" t="s">
         <v>538</v>
       </c>
       <c r="J134" s="7">
-        <v>1</v>
-      </c>
-      <c r="K134" s="17" t="s">
-        <v>546</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K134" s="7"/>
       <c r="U134" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="36.75" thickBot="1">
+    <row r="135" spans="1:21" ht="64.5" thickBot="1">
       <c r="B135" s="11">
-        <f t="shared" ref="B135:B138" si="4">ROW(B135) - ROW($B$2)</f>
+        <f>ROW(B135) - ROW($B$2)</f>
         <v>133</v>
       </c>
       <c r="C135" s="12" t="s">
@@ -7142,33 +7150,35 @@
       <c r="D135" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="E135" s="10" t="s">
-        <v>549</v>
+      <c r="E135" s="8" t="s">
+        <v>544</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="G135" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="I135" s="10" t="s">
+      <c r="G135" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="I135" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J135" s="9">
-        <v>1</v>
-      </c>
-      <c r="K135" s="9"/>
+      <c r="J135" s="7">
+        <v>1</v>
+      </c>
+      <c r="K135" s="17" t="s">
+        <v>546</v>
+      </c>
       <c r="U135" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="24.75" thickBot="1">
+    <row r="136" spans="1:21" ht="36.75" thickBot="1">
       <c r="B136" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="B136:B139" si="4">ROW(B136) - ROW($B$2)</f>
         <v>134</v>
       </c>
       <c r="C136" s="12" t="s">
@@ -7178,22 +7188,22 @@
         <v>538</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>537</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>538</v>
       </c>
       <c r="J136" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K136" s="9"/>
       <c r="U136" t="b">
@@ -7201,7 +7211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="36.75" thickBot="1">
+    <row r="137" spans="1:21" ht="24.75" thickBot="1">
       <c r="B137" s="11">
         <f t="shared" si="4"/>
         <v>135</v>
@@ -7213,32 +7223,30 @@
         <v>538</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>537</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="I137" s="10" t="s">
         <v>538</v>
       </c>
       <c r="J137" s="9">
-        <v>1</v>
-      </c>
-      <c r="K137" s="18" t="s">
-        <v>561</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K137" s="9"/>
       <c r="U137" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="24.75" thickBot="1">
+    <row r="138" spans="1:21" ht="36.75" thickBot="1">
       <c r="B138" s="11">
         <f t="shared" si="4"/>
         <v>136</v>
@@ -7250,16 +7258,16 @@
         <v>538</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>537</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="I138" s="10" t="s">
         <v>538</v>
@@ -7268,9 +7276,46 @@
         <v>1</v>
       </c>
       <c r="K138" s="18" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="U138" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" ht="24.75" thickBot="1">
+      <c r="B139" s="11">
+        <f t="shared" si="4"/>
+        <v>137</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="I139" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J139" s="9">
+        <v>1</v>
+      </c>
+      <c r="K139" s="18" t="s">
+        <v>568</v>
+      </c>
+      <c r="U139" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7280,8 +7325,8 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K137" r:id="rId1" location="nav-specification"/>
-    <hyperlink ref="K138" r:id="rId2"/>
+    <hyperlink ref="K138" r:id="rId1" location="nav-specification"/>
+    <hyperlink ref="K139" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
